--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1970"/>
+  <dimension ref="A1:L1975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83066,6 +83066,206 @@
         </is>
       </c>
     </row>
+    <row r="1971">
+      <c r="A1971" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C1971" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1971" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1971" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F1971" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="G1971" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1971" t="inlineStr"/>
+      <c r="I1971" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J1971" t="n">
+        <v>190</v>
+      </c>
+      <c r="K1971" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="L1971" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C1972" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1972" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1972" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="F1972" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="G1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1972" t="inlineStr"/>
+      <c r="I1972" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J1972" t="n">
+        <v>135</v>
+      </c>
+      <c r="K1972" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L1972" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C1973" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1973" t="n">
+        <v>28</v>
+      </c>
+      <c r="E1973" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F1973" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="G1973" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1973" t="inlineStr"/>
+      <c r="I1973" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J1973" t="n">
+        <v>67</v>
+      </c>
+      <c r="K1973" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="L1973" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C1974" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1974" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1974" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F1974" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="G1974" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1974" t="inlineStr"/>
+      <c r="I1974" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J1974" t="n">
+        <v>92</v>
+      </c>
+      <c r="K1974" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="L1974" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C1975" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1975" t="n">
+        <v>34</v>
+      </c>
+      <c r="E1975" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F1975" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="G1975" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H1975" t="inlineStr"/>
+      <c r="I1975" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J1975" t="n">
+        <v>109</v>
+      </c>
+      <c r="K1975" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="L1975" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1975"/>
+  <dimension ref="A1:L1980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83266,6 +83266,206 @@
         </is>
       </c>
     </row>
+    <row r="1976">
+      <c r="A1976" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C1976" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1976" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1976" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F1976" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="G1976" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1976" t="inlineStr"/>
+      <c r="I1976" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J1976" t="n">
+        <v>205</v>
+      </c>
+      <c r="K1976" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="L1976" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C1977" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1977" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1977" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="F1977" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="G1977" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1977" t="inlineStr"/>
+      <c r="I1977" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J1977" t="n">
+        <v>151</v>
+      </c>
+      <c r="K1977" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="L1977" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C1978" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1978" t="n">
+        <v>29</v>
+      </c>
+      <c r="E1978" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="F1978" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="G1978" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1978" t="inlineStr"/>
+      <c r="I1978" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J1978" t="n">
+        <v>54</v>
+      </c>
+      <c r="K1978" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="L1978" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C1979" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1979" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1979" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="F1979" t="n">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="G1979" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1979" t="inlineStr"/>
+      <c r="I1979" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J1979" t="n">
+        <v>89</v>
+      </c>
+      <c r="K1979" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="L1979" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C1980" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1980" t="n">
+        <v>34</v>
+      </c>
+      <c r="E1980" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F1980" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="G1980" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1980" t="inlineStr"/>
+      <c r="I1980" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J1980" t="n">
+        <v>106</v>
+      </c>
+      <c r="K1980" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="L1980" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1980"/>
+  <dimension ref="A1:L1985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83466,6 +83466,206 @@
         </is>
       </c>
     </row>
+    <row r="1981">
+      <c r="A1981" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C1981" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1981" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1981" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F1981" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="G1981" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1981" t="inlineStr"/>
+      <c r="I1981" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1981" t="n">
+        <v>109</v>
+      </c>
+      <c r="K1981" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="L1981" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C1982" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1982" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1982" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F1982" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="G1982" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1982" t="inlineStr"/>
+      <c r="I1982" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1982" t="n">
+        <v>116</v>
+      </c>
+      <c r="K1982" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="L1982" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C1983" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1983" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1983" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F1983" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G1983" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1983" t="inlineStr"/>
+      <c r="I1983" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1983" t="n">
+        <v>105</v>
+      </c>
+      <c r="K1983" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="L1983" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C1984" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1984" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1984" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F1984" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="G1984" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1984" t="inlineStr"/>
+      <c r="I1984" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1984" t="n">
+        <v>113</v>
+      </c>
+      <c r="K1984" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="L1984" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C1985" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1985" t="n">
+        <v>34</v>
+      </c>
+      <c r="E1985" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F1985" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="G1985" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1985" t="inlineStr"/>
+      <c r="I1985" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1985" t="n">
+        <v>112</v>
+      </c>
+      <c r="K1985" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="L1985" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1985"/>
+  <dimension ref="A1:L1990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83666,6 +83666,206 @@
         </is>
       </c>
     </row>
+    <row r="1986">
+      <c r="A1986" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C1986" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1986" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1986" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="F1986" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="G1986" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1986" t="inlineStr"/>
+      <c r="I1986" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1986" t="n">
+        <v>127</v>
+      </c>
+      <c r="K1986" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="L1986" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C1987" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1987" t="n">
+        <v>29</v>
+      </c>
+      <c r="E1987" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="F1987" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="G1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1987" t="inlineStr"/>
+      <c r="I1987" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1987" t="n">
+        <v>135</v>
+      </c>
+      <c r="K1987" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L1987" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C1988" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1988" t="n">
+        <v>28</v>
+      </c>
+      <c r="E1988" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="F1988" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G1988" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H1988" t="inlineStr"/>
+      <c r="I1988" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1988" t="n">
+        <v>109</v>
+      </c>
+      <c r="K1988" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="L1988" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C1989" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1989" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="F1989" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G1989" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1989" t="inlineStr"/>
+      <c r="I1989" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1989" t="n">
+        <v>105</v>
+      </c>
+      <c r="K1989" t="n">
+        <v>12</v>
+      </c>
+      <c r="L1989" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C1990" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1990" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1990" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="F1990" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G1990" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1990" t="inlineStr"/>
+      <c r="I1990" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1990" t="n">
+        <v>100</v>
+      </c>
+      <c r="K1990" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="L1990" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1990"/>
+  <dimension ref="A1:L1995"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83866,6 +83866,206 @@
         </is>
       </c>
     </row>
+    <row r="1991">
+      <c r="A1991" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C1991" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1991" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1991" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>72</v>
+      </c>
+      <c r="G1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1991" t="inlineStr"/>
+      <c r="I1991" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1991" t="n">
+        <v>114</v>
+      </c>
+      <c r="K1991" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="L1991" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C1992" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>29</v>
+      </c>
+      <c r="E1992" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="G1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1992" t="inlineStr"/>
+      <c r="I1992" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1992" t="n">
+        <v>114</v>
+      </c>
+      <c r="K1992" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="L1992" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C1993" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>28</v>
+      </c>
+      <c r="E1993" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F1993" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="G1993" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H1993" t="inlineStr"/>
+      <c r="I1993" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1993" t="n">
+        <v>105</v>
+      </c>
+      <c r="K1993" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="L1993" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C1994" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1994" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F1994" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="G1994" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1994" t="inlineStr"/>
+      <c r="I1994" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1994" t="n">
+        <v>103</v>
+      </c>
+      <c r="K1994" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="L1994" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C1995" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1995" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1995" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F1995" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="G1995" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1995" t="inlineStr"/>
+      <c r="I1995" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J1995" t="n">
+        <v>103</v>
+      </c>
+      <c r="K1995" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="L1995" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1995"/>
+  <dimension ref="A1:L2000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84066,6 +84066,206 @@
         </is>
       </c>
     </row>
+    <row r="1996">
+      <c r="A1996" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C1996" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1996" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="F1996" t="n">
+        <v>75.43000000000001</v>
+      </c>
+      <c r="G1996" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H1996" t="inlineStr"/>
+      <c r="I1996" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J1996" t="n">
+        <v>112</v>
+      </c>
+      <c r="K1996" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="L1996" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C1997" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1997" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="G1997" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1997" t="inlineStr"/>
+      <c r="I1997" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J1997" t="n">
+        <v>135</v>
+      </c>
+      <c r="K1997" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="L1997" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C1998" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>29</v>
+      </c>
+      <c r="E1998" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F1998" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="G1998" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1998" t="inlineStr"/>
+      <c r="I1998" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J1998" t="n">
+        <v>112</v>
+      </c>
+      <c r="K1998" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L1998" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C1999" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1999" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="F1999" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="G1999" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1999" t="inlineStr"/>
+      <c r="I1999" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J1999" t="n">
+        <v>112</v>
+      </c>
+      <c r="K1999" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="L1999" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2000" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2000" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="F2000" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="G2000" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H2000" t="inlineStr"/>
+      <c r="I2000" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2000" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2000" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L2000" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2000"/>
+  <dimension ref="A1:L2005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84266,6 +84266,206 @@
         </is>
       </c>
     </row>
+    <row r="2001">
+      <c r="A2001" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2001" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F2001" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="G2001" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H2001" t="inlineStr"/>
+      <c r="I2001" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J2001" t="n">
+        <v>185</v>
+      </c>
+      <c r="K2001" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L2001" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2002" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F2002" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="G2002" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H2002" t="inlineStr"/>
+      <c r="I2002" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J2002" t="n">
+        <v>145</v>
+      </c>
+      <c r="K2002" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="L2002" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2003" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2003" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="F2003" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="G2003" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H2003" t="inlineStr"/>
+      <c r="I2003" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2003" t="n">
+        <v>28</v>
+      </c>
+      <c r="K2003" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="L2003" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2004" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2004" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F2004" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G2004" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2004" t="inlineStr"/>
+      <c r="I2004" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2004" t="n">
+        <v>83</v>
+      </c>
+      <c r="K2004" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L2004" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2005" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2005" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="F2005" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="G2005" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2005" t="inlineStr"/>
+      <c r="I2005" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2005" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2005" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="L2005" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2005"/>
+  <dimension ref="A1:L2010"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84466,6 +84466,206 @@
         </is>
       </c>
     </row>
+    <row r="2006">
+      <c r="A2006" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2006" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2006" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="F2006" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="G2006" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H2006" t="inlineStr"/>
+      <c r="I2006" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2006" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2006" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L2006" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2007" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="G2007" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2007" t="inlineStr"/>
+      <c r="I2007" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2007" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2007" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="L2007" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2008" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="G2008" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2008" t="inlineStr"/>
+      <c r="I2008" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2008" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2008" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="L2008" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2009" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2009" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="F2009" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="G2009" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H2009" t="inlineStr"/>
+      <c r="I2009" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2009" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2009" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="L2009" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2010" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="G2010" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2010" t="inlineStr"/>
+      <c r="I2010" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2010" t="n">
+        <v>115</v>
+      </c>
+      <c r="K2010" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2010" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2010"/>
+  <dimension ref="A1:L2015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84666,6 +84666,206 @@
         </is>
       </c>
     </row>
+    <row r="2011">
+      <c r="A2011" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2011" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2011" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F2011" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G2011" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2011" t="inlineStr"/>
+      <c r="I2011" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J2011" t="n">
+        <v>197</v>
+      </c>
+      <c r="K2011" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="L2011" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2012" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2012" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="G2012" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2012" t="inlineStr"/>
+      <c r="I2012" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="J2012" t="n">
+        <v>124</v>
+      </c>
+      <c r="K2012" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L2012" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2013" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2013" t="inlineStr"/>
+      <c r="I2013" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2013" t="n">
+        <v>32</v>
+      </c>
+      <c r="K2013" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="L2013" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2014" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2014" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>77.33</v>
+      </c>
+      <c r="G2014" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2014" t="inlineStr"/>
+      <c r="I2014" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J2014" t="n">
+        <v>64</v>
+      </c>
+      <c r="K2014" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="L2014" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2015" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="G2015" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2015" t="inlineStr"/>
+      <c r="I2015" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J2015" t="n">
+        <v>67</v>
+      </c>
+      <c r="K2015" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="L2015" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2015"/>
+  <dimension ref="A1:L2020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84866,6 +84866,206 @@
         </is>
       </c>
     </row>
+    <row r="2016">
+      <c r="A2016" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2016" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2016" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="G2016" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2016" t="inlineStr"/>
+      <c r="I2016" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J2016" t="n">
+        <v>198</v>
+      </c>
+      <c r="K2016" t="n">
+        <v>14</v>
+      </c>
+      <c r="L2016" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2017" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="G2017" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2017" t="inlineStr"/>
+      <c r="I2017" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J2017" t="n">
+        <v>141</v>
+      </c>
+      <c r="K2017" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="L2017" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2018" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="G2018" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2018" t="inlineStr"/>
+      <c r="I2018" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J2018" t="n">
+        <v>27</v>
+      </c>
+      <c r="K2018" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="L2018" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2019" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2019" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="G2019" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2019" t="inlineStr"/>
+      <c r="I2019" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J2019" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2019" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="L2019" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2020" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="G2020" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2020" t="inlineStr"/>
+      <c r="I2020" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J2020" t="n">
+        <v>88</v>
+      </c>
+      <c r="K2020" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="L2020" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2020"/>
+  <dimension ref="A1:L2025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85066,6 +85066,206 @@
         </is>
       </c>
     </row>
+    <row r="2021">
+      <c r="A2021" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2021" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2021" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>73</v>
+      </c>
+      <c r="G2021" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2021" t="inlineStr"/>
+      <c r="I2021" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J2021" t="n">
+        <v>188</v>
+      </c>
+      <c r="K2021" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="L2021" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2022" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2022" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F2022" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="G2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2022" t="inlineStr"/>
+      <c r="I2022" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J2022" t="n">
+        <v>141</v>
+      </c>
+      <c r="K2022" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="L2022" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2023" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2023" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="G2023" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2023" t="inlineStr"/>
+      <c r="I2023" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J2023" t="n">
+        <v>44</v>
+      </c>
+      <c r="K2023" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="L2023" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2024" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2024" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G2024" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2024" t="inlineStr"/>
+      <c r="I2024" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J2024" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2024" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L2024" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2025" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2025" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2025" t="inlineStr"/>
+      <c r="I2025" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2025" t="n">
+        <v>108</v>
+      </c>
+      <c r="K2025" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="L2025" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2025"/>
+  <dimension ref="A1:L2030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85266,6 +85266,206 @@
         </is>
       </c>
     </row>
+    <row r="2026">
+      <c r="A2026" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2026" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2026" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F2026" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2026" t="inlineStr"/>
+      <c r="I2026" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J2026" t="n">
+        <v>180</v>
+      </c>
+      <c r="K2026" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="L2026" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2027" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2027" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="G2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2027" t="inlineStr"/>
+      <c r="I2027" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2027" t="n">
+        <v>126</v>
+      </c>
+      <c r="K2027" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="L2027" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2028" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2028" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="G2028" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2028" t="inlineStr"/>
+      <c r="I2028" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2028" t="n">
+        <v>115</v>
+      </c>
+      <c r="K2028" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="L2028" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2029" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2029" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="G2029" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2029" t="inlineStr"/>
+      <c r="I2029" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2029" t="n">
+        <v>151</v>
+      </c>
+      <c r="K2029" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="L2029" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2030" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2030" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="G2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2030" t="inlineStr"/>
+      <c r="I2030" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2030" t="n">
+        <v>120</v>
+      </c>
+      <c r="K2030" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="L2030" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2030"/>
+  <dimension ref="A1:L2035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85466,6 +85466,206 @@
         </is>
       </c>
     </row>
+    <row r="2031">
+      <c r="A2031" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2031" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2031" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2031" t="n">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="G2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2031" t="inlineStr"/>
+      <c r="I2031" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J2031" t="n">
+        <v>180</v>
+      </c>
+      <c r="K2031" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="L2031" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2032" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2032" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="G2032" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2032" t="inlineStr"/>
+      <c r="I2032" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J2032" t="n">
+        <v>137</v>
+      </c>
+      <c r="K2032" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="L2032" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2033" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2033" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F2033" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="G2033" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2033" t="inlineStr"/>
+      <c r="I2033" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J2033" t="n">
+        <v>36</v>
+      </c>
+      <c r="K2033" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2033" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2034" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2034" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="G2034" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2034" t="inlineStr"/>
+      <c r="I2034" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J2034" t="n">
+        <v>99</v>
+      </c>
+      <c r="K2034" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="L2034" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2035" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2035" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F2035" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G2035" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2035" t="inlineStr"/>
+      <c r="I2035" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J2035" t="n">
+        <v>94</v>
+      </c>
+      <c r="K2035" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="L2035" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2035"/>
+  <dimension ref="A1:L2040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85666,6 +85666,206 @@
         </is>
       </c>
     </row>
+    <row r="2036">
+      <c r="A2036" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2036" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2036" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="F2036" t="n">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="G2036" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2036" t="inlineStr"/>
+      <c r="I2036" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J2036" t="n">
+        <v>185</v>
+      </c>
+      <c r="K2036" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="L2036" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2037" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2037" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="F2037" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="G2037" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2037" t="inlineStr"/>
+      <c r="I2037" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2037" t="n">
+        <v>137</v>
+      </c>
+      <c r="K2037" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="L2037" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2038" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2038" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F2038" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="G2038" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2038" t="inlineStr"/>
+      <c r="I2038" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J2038" t="n">
+        <v>36</v>
+      </c>
+      <c r="K2038" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L2038" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2039" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2039" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2039" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="G2039" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2039" t="inlineStr"/>
+      <c r="I2039" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J2039" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2039" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="L2039" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2040" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2040" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F2040" t="n">
+        <v>70</v>
+      </c>
+      <c r="G2040" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2040" t="inlineStr"/>
+      <c r="I2040" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J2040" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2040" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="L2040" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2040"/>
+  <dimension ref="A1:L2045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85866,6 +85866,206 @@
         </is>
       </c>
     </row>
+    <row r="2041">
+      <c r="A2041" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2041" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2041" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F2041" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="G2041" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2041" t="inlineStr"/>
+      <c r="I2041" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J2041" t="n">
+        <v>201</v>
+      </c>
+      <c r="K2041" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="L2041" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2042" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2042" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F2042" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="G2042" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H2042" t="inlineStr"/>
+      <c r="I2042" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J2042" t="n">
+        <v>139</v>
+      </c>
+      <c r="K2042" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2042" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2043" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2043" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F2043" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="G2043" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H2043" t="inlineStr"/>
+      <c r="I2043" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J2043" t="n">
+        <v>42</v>
+      </c>
+      <c r="K2043" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L2043" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2044" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2044" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="F2044" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="G2044" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2044" t="inlineStr"/>
+      <c r="I2044" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J2044" t="n">
+        <v>94</v>
+      </c>
+      <c r="K2044" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="L2044" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2045" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2045" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F2045" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="G2045" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2045" t="inlineStr"/>
+      <c r="I2045" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J2045" t="n">
+        <v>110</v>
+      </c>
+      <c r="K2045" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="L2045" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2045"/>
+  <dimension ref="A1:L2050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86066,6 +86066,206 @@
         </is>
       </c>
     </row>
+    <row r="2046">
+      <c r="A2046" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2046" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2046" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F2046" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="G2046" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H2046" t="inlineStr"/>
+      <c r="I2046" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2046" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2046" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L2046" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2047" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2047" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F2047" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G2047" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H2047" t="inlineStr"/>
+      <c r="I2047" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2047" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2047" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="L2047" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2048" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2048" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F2048" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G2048" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2048" t="inlineStr"/>
+      <c r="I2048" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2048" t="n">
+        <v>109</v>
+      </c>
+      <c r="K2048" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L2048" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2049" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2049" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="F2049" t="n">
+        <v>75.43000000000001</v>
+      </c>
+      <c r="G2049" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H2049" t="inlineStr"/>
+      <c r="I2049" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2049" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2049" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="L2049" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2050" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2050" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F2050" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="G2050" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2050" t="inlineStr"/>
+      <c r="I2050" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2050" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2050" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="L2050" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2050"/>
+  <dimension ref="A1:L2055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86266,6 +86266,206 @@
         </is>
       </c>
     </row>
+    <row r="2051">
+      <c r="A2051" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2051" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2051" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2051" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="F2051" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="G2051" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H2051" t="inlineStr"/>
+      <c r="I2051" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J2051" t="n">
+        <v>185</v>
+      </c>
+      <c r="K2051" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="L2051" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2052" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2052" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F2052" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="G2052" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H2052" t="inlineStr"/>
+      <c r="I2052" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J2052" t="n">
+        <v>171</v>
+      </c>
+      <c r="K2052" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="L2052" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2053" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2053" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="F2053" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="G2053" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2053" t="inlineStr"/>
+      <c r="I2053" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J2053" t="n">
+        <v>68</v>
+      </c>
+      <c r="K2053" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L2053" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2054" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2054" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F2054" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="G2054" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H2054" t="inlineStr"/>
+      <c r="I2054" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J2054" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2054" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="L2054" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2055" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2055" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2055" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="G2055" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2055" t="inlineStr"/>
+      <c r="I2055" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J2055" t="n">
+        <v>110</v>
+      </c>
+      <c r="K2055" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="L2055" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2055"/>
+  <dimension ref="A1:L2060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86466,6 +86466,206 @@
         </is>
       </c>
     </row>
+    <row r="2056">
+      <c r="A2056" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2056" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2056" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="F2056" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="G2056" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2056" t="inlineStr"/>
+      <c r="I2056" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2056" t="n">
+        <v>201</v>
+      </c>
+      <c r="K2056" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="L2056" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2057" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2057" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="G2057" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2057" t="inlineStr"/>
+      <c r="I2057" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J2057" t="n">
+        <v>151</v>
+      </c>
+      <c r="K2057" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="L2057" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2058" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2058" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2058" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="F2058" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="G2058" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2058" t="inlineStr"/>
+      <c r="I2058" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2058" t="n">
+        <v>63</v>
+      </c>
+      <c r="K2058" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L2058" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2059" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="G2059" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H2059" t="inlineStr"/>
+      <c r="I2059" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2059" t="n">
+        <v>97</v>
+      </c>
+      <c r="K2059" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="L2059" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2060" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2060" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>76</v>
+      </c>
+      <c r="G2060" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H2060" t="inlineStr"/>
+      <c r="I2060" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2060" t="n">
+        <v>104</v>
+      </c>
+      <c r="K2060" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="L2060" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2060"/>
+  <dimension ref="A1:L2065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86666,6 +86666,206 @@
         </is>
       </c>
     </row>
+    <row r="2061">
+      <c r="A2061" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2061" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="G2061" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2061" t="inlineStr"/>
+      <c r="I2061" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J2061" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2061" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="L2061" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2062" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2062" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="G2062" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H2062" t="inlineStr"/>
+      <c r="I2062" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J2062" t="n">
+        <v>147</v>
+      </c>
+      <c r="K2062" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L2062" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2063" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="G2063" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2063" t="inlineStr"/>
+      <c r="I2063" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J2063" t="n">
+        <v>37</v>
+      </c>
+      <c r="K2063" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="L2063" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2064" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2064" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="G2064" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2064" t="inlineStr"/>
+      <c r="I2064" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J2064" t="n">
+        <v>93</v>
+      </c>
+      <c r="K2064" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="L2064" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2065" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2065" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="F2065" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="G2065" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2065" t="inlineStr"/>
+      <c r="I2065" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J2065" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2065" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="L2065" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2065"/>
+  <dimension ref="A1:L2070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86866,6 +86866,206 @@
         </is>
       </c>
     </row>
+    <row r="2066">
+      <c r="A2066" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2066" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="G2066" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2066" t="inlineStr"/>
+      <c r="I2066" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J2066" t="n">
+        <v>179</v>
+      </c>
+      <c r="K2066" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="L2066" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2067" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>83.23999999999999</v>
+      </c>
+      <c r="G2067" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H2067" t="inlineStr"/>
+      <c r="I2067" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="J2067" t="n">
+        <v>141</v>
+      </c>
+      <c r="K2067" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="L2067" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2068" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>78.81</v>
+      </c>
+      <c r="G2068" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2068" t="inlineStr"/>
+      <c r="I2068" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2068" t="n">
+        <v>54</v>
+      </c>
+      <c r="K2068" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="L2068" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2069" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G2069" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H2069" t="inlineStr"/>
+      <c r="I2069" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2069" t="n">
+        <v>89</v>
+      </c>
+      <c r="K2069" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="L2069" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2070" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="G2070" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2070" t="inlineStr"/>
+      <c r="I2070" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2070" t="n">
+        <v>101</v>
+      </c>
+      <c r="K2070" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="L2070" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2070"/>
+  <dimension ref="A1:L2075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87066,6 +87066,206 @@
         </is>
       </c>
     </row>
+    <row r="2071">
+      <c r="A2071" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2071" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="G2071" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H2071" t="inlineStr"/>
+      <c r="I2071" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J2071" t="n">
+        <v>196</v>
+      </c>
+      <c r="K2071" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="L2071" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2072" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="G2072" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H2072" t="inlineStr"/>
+      <c r="I2072" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="J2072" t="n">
+        <v>143</v>
+      </c>
+      <c r="K2072" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="L2072" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2073" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>81</v>
+      </c>
+      <c r="G2073" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H2073" t="inlineStr"/>
+      <c r="I2073" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2073" t="n">
+        <v>43</v>
+      </c>
+      <c r="K2073" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L2073" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2074" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="G2074" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2074" t="inlineStr"/>
+      <c r="I2074" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J2074" t="n">
+        <v>89</v>
+      </c>
+      <c r="K2074" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="L2074" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2075" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="G2075" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2075" t="inlineStr"/>
+      <c r="I2075" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J2075" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2075" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L2075" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2075"/>
+  <dimension ref="A1:L2080"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87266,6 +87266,206 @@
         </is>
       </c>
     </row>
+    <row r="2076">
+      <c r="A2076" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2076" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G2076" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2076" t="inlineStr"/>
+      <c r="I2076" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J2076" t="n">
+        <v>189</v>
+      </c>
+      <c r="K2076" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="L2076" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2077" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="G2077" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H2077" t="inlineStr"/>
+      <c r="I2077" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J2077" t="n">
+        <v>134</v>
+      </c>
+      <c r="K2077" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="L2077" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2078" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>81.55</v>
+      </c>
+      <c r="G2078" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2078" t="inlineStr"/>
+      <c r="I2078" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J2078" t="n">
+        <v>39</v>
+      </c>
+      <c r="K2078" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="L2078" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2079" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="G2079" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2079" t="inlineStr"/>
+      <c r="I2079" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J2079" t="n">
+        <v>94</v>
+      </c>
+      <c r="K2079" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="L2079" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2080" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="G2080" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2080" t="inlineStr"/>
+      <c r="I2080" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J2080" t="n">
+        <v>97</v>
+      </c>
+      <c r="K2080" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2080" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2080"/>
+  <dimension ref="A1:L2085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87466,6 +87466,206 @@
         </is>
       </c>
     </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2081" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="G2081" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2081" t="inlineStr"/>
+      <c r="I2081" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2081" t="n">
+        <v>178</v>
+      </c>
+      <c r="K2081" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="L2081" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2082" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2082" t="inlineStr"/>
+      <c r="I2082" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2082" t="n">
+        <v>139</v>
+      </c>
+      <c r="K2082" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="L2082" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2083" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H2083" t="inlineStr"/>
+      <c r="I2083" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2083" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2083" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="L2083" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2084" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2084" t="inlineStr"/>
+      <c r="I2084" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2084" t="n">
+        <v>89</v>
+      </c>
+      <c r="K2084" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="L2084" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2085" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2085" t="inlineStr"/>
+      <c r="I2085" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2085" t="n">
+        <v>97</v>
+      </c>
+      <c r="K2085" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="L2085" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2085"/>
+  <dimension ref="A1:L2090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87666,6 +87666,206 @@
         </is>
       </c>
     </row>
+    <row r="2086">
+      <c r="A2086" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2086" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2086" t="inlineStr"/>
+      <c r="I2086" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2086" t="n">
+        <v>177</v>
+      </c>
+      <c r="K2086" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="L2086" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2087" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2087" t="inlineStr"/>
+      <c r="I2087" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2087" t="n">
+        <v>148</v>
+      </c>
+      <c r="K2087" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="L2087" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2088" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2088" t="inlineStr"/>
+      <c r="I2088" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2088" t="n">
+        <v>32</v>
+      </c>
+      <c r="K2088" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="L2088" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2089" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>64</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2089" t="inlineStr"/>
+      <c r="I2089" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2089" t="n">
+        <v>102</v>
+      </c>
+      <c r="K2089" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="L2089" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2090" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2090" t="inlineStr"/>
+      <c r="I2090" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2090" t="n">
+        <v>68</v>
+      </c>
+      <c r="K2090" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="L2090" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2090"/>
+  <dimension ref="A1:L2095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87866,6 +87866,206 @@
         </is>
       </c>
     </row>
+    <row r="2091">
+      <c r="A2091" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2091" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2091" t="inlineStr"/>
+      <c r="I2091" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J2091" t="n">
+        <v>182</v>
+      </c>
+      <c r="K2091" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="L2091" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2092" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2092" t="inlineStr"/>
+      <c r="I2092" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J2092" t="n">
+        <v>158</v>
+      </c>
+      <c r="K2092" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="L2092" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2093" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2093" t="inlineStr"/>
+      <c r="I2093" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J2093" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2093" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="L2093" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2094" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2094" t="inlineStr"/>
+      <c r="I2094" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J2094" t="n">
+        <v>95</v>
+      </c>
+      <c r="K2094" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L2094" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2095" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2095" t="inlineStr"/>
+      <c r="I2095" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J2095" t="n">
+        <v>80</v>
+      </c>
+      <c r="K2095" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="L2095" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2095"/>
+  <dimension ref="A1:L2100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88066,6 +88066,206 @@
         </is>
       </c>
     </row>
+    <row r="2096">
+      <c r="A2096" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2096" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2096" t="inlineStr"/>
+      <c r="I2096" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="J2096" t="n">
+        <v>180</v>
+      </c>
+      <c r="K2096" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="L2096" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2097" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="G2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2097" t="inlineStr"/>
+      <c r="I2097" t="n">
+        <v>15</v>
+      </c>
+      <c r="J2097" t="n">
+        <v>170</v>
+      </c>
+      <c r="K2097" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="L2097" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2098" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2098" t="inlineStr"/>
+      <c r="I2098" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J2098" t="n">
+        <v>28</v>
+      </c>
+      <c r="K2098" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="L2098" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2099" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2099" t="inlineStr"/>
+      <c r="I2099" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2099" t="n">
+        <v>89</v>
+      </c>
+      <c r="K2099" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="L2099" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2100" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2100" t="inlineStr"/>
+      <c r="I2100" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J2100" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2100" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="L2100" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2100"/>
+  <dimension ref="A1:L2105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88266,6 +88266,206 @@
         </is>
       </c>
     </row>
+    <row r="2101">
+      <c r="A2101" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2101" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2101" t="inlineStr"/>
+      <c r="I2101" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J2101" t="n">
+        <v>175</v>
+      </c>
+      <c r="K2101" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="L2101" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2102" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2102" t="inlineStr"/>
+      <c r="I2102" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J2102" t="n">
+        <v>178</v>
+      </c>
+      <c r="K2102" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="L2102" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2103" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2103" t="inlineStr"/>
+      <c r="I2103" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J2103" t="n">
+        <v>43</v>
+      </c>
+      <c r="K2103" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="L2103" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2104" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>67</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2104" t="inlineStr"/>
+      <c r="I2104" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J2104" t="n">
+        <v>103</v>
+      </c>
+      <c r="K2104" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2104" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2105" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2105" t="inlineStr"/>
+      <c r="I2105" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J2105" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2105" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="L2105" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2105"/>
+  <dimension ref="A1:L2110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88466,6 +88466,206 @@
         </is>
       </c>
     </row>
+    <row r="2106">
+      <c r="A2106" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2106" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>73.52</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2106" t="inlineStr"/>
+      <c r="I2106" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="J2106" t="n">
+        <v>184</v>
+      </c>
+      <c r="K2106" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="L2106" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2107" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>79.62</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2107" t="inlineStr"/>
+      <c r="I2107" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J2107" t="n">
+        <v>166</v>
+      </c>
+      <c r="K2107" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="L2107" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2108" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>72.81</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2108" t="inlineStr"/>
+      <c r="I2108" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J2108" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2108" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="L2108" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2109" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2109" t="inlineStr"/>
+      <c r="I2109" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J2109" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2109" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="L2109" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2110" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2110" t="inlineStr"/>
+      <c r="I2110" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J2110" t="n">
+        <v>113</v>
+      </c>
+      <c r="K2110" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="L2110" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2110"/>
+  <dimension ref="A1:L2115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88666,6 +88666,206 @@
         </is>
       </c>
     </row>
+    <row r="2111">
+      <c r="A2111" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2111" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2111" t="inlineStr"/>
+      <c r="I2111" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J2111" t="n">
+        <v>187</v>
+      </c>
+      <c r="K2111" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="L2111" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2112" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2112" t="inlineStr"/>
+      <c r="I2112" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J2112" t="n">
+        <v>151</v>
+      </c>
+      <c r="K2112" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L2112" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2113" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2113" t="inlineStr"/>
+      <c r="I2113" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J2113" t="n">
+        <v>46</v>
+      </c>
+      <c r="K2113" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2113" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2114" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2114" t="inlineStr"/>
+      <c r="I2114" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J2114" t="n">
+        <v>89</v>
+      </c>
+      <c r="K2114" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="L2114" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2115" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>71</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2115" t="inlineStr"/>
+      <c r="I2115" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2115" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2115" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="L2115" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2115"/>
+  <dimension ref="A1:L2120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88866,6 +88866,206 @@
         </is>
       </c>
     </row>
+    <row r="2116">
+      <c r="A2116" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2116" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2116" t="inlineStr"/>
+      <c r="I2116" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2116" t="n">
+        <v>211</v>
+      </c>
+      <c r="K2116" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="L2116" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2117" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2117" t="inlineStr"/>
+      <c r="I2117" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2117" t="n">
+        <v>150</v>
+      </c>
+      <c r="K2117" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L2117" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2118" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2118" t="inlineStr"/>
+      <c r="I2118" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2118" t="n">
+        <v>54</v>
+      </c>
+      <c r="K2118" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="L2118" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2119" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2119" t="inlineStr"/>
+      <c r="I2119" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2119" t="n">
+        <v>96</v>
+      </c>
+      <c r="K2119" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L2119" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2120" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2120" t="inlineStr"/>
+      <c r="I2120" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2120" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2120" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="L2120" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2120"/>
+  <dimension ref="A1:L2125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89066,6 +89066,206 @@
         </is>
       </c>
     </row>
+    <row r="2121">
+      <c r="A2121" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2121" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2121" t="inlineStr"/>
+      <c r="I2121" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2121" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2121" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2121" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2122" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>79.62</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2122" t="inlineStr"/>
+      <c r="I2122" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2122" t="n">
+        <v>166</v>
+      </c>
+      <c r="K2122" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="L2122" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2123" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2123" t="inlineStr"/>
+      <c r="I2123" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2123" t="n">
+        <v>53</v>
+      </c>
+      <c r="K2123" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="L2123" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2124" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2124" t="inlineStr"/>
+      <c r="I2124" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2124" t="n">
+        <v>102</v>
+      </c>
+      <c r="K2124" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="L2124" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2125" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2125" t="inlineStr"/>
+      <c r="I2125" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2125" t="n">
+        <v>110</v>
+      </c>
+      <c r="K2125" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="L2125" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2125"/>
+  <dimension ref="A1:L2130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89266,6 +89266,206 @@
         </is>
       </c>
     </row>
+    <row r="2126">
+      <c r="A2126" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2126" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2126" t="inlineStr"/>
+      <c r="I2126" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="J2126" t="n">
+        <v>183</v>
+      </c>
+      <c r="K2126" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="L2126" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2127" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="G2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2127" t="inlineStr"/>
+      <c r="I2127" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J2127" t="n">
+        <v>140</v>
+      </c>
+      <c r="K2127" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="L2127" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2128" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2128" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2128" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="G2128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2128" t="inlineStr"/>
+      <c r="I2128" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J2128" t="n">
+        <v>252</v>
+      </c>
+      <c r="K2128" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="L2128" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2129" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="G2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2129" t="inlineStr"/>
+      <c r="I2129" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J2129" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2129" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="L2129" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2130" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2130" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="F2130" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="G2130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2130" t="inlineStr"/>
+      <c r="I2130" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2130" t="n">
+        <v>102</v>
+      </c>
+      <c r="K2130" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="L2130" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2130"/>
+  <dimension ref="A1:L2135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89466,6 +89466,206 @@
         </is>
       </c>
     </row>
+    <row r="2131">
+      <c r="A2131" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2131" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2131" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F2131" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="G2131" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2131" t="inlineStr"/>
+      <c r="I2131" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="J2131" t="n">
+        <v>127</v>
+      </c>
+      <c r="K2131" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="L2131" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2132" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2132" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="G2132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2132" t="inlineStr"/>
+      <c r="I2132" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="J2132" t="n">
+        <v>129</v>
+      </c>
+      <c r="K2132" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="L2132" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2133" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2133" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="F2133" t="n">
+        <v>74.05</v>
+      </c>
+      <c r="G2133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2133" t="inlineStr"/>
+      <c r="I2133" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2133" t="n">
+        <v>125</v>
+      </c>
+      <c r="K2133" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="L2133" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2134" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2134" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2134" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G2134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2134" t="inlineStr"/>
+      <c r="I2134" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2134" t="n">
+        <v>124</v>
+      </c>
+      <c r="K2134" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L2134" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2135" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2135" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2135" t="n">
+        <v>62.65</v>
+      </c>
+      <c r="G2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2135" t="inlineStr"/>
+      <c r="I2135" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2135" t="n">
+        <v>121</v>
+      </c>
+      <c r="K2135" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="L2135" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2135"/>
+  <dimension ref="A1:L2140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89666,6 +89666,206 @@
         </is>
       </c>
     </row>
+    <row r="2136">
+      <c r="A2136" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2136" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2136" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="F2136" t="n">
+        <v>65.43000000000001</v>
+      </c>
+      <c r="G2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2136" t="inlineStr"/>
+      <c r="I2136" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J2136" t="n">
+        <v>185</v>
+      </c>
+      <c r="K2136" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="L2136" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2137" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2137" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F2137" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="G2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2137" t="inlineStr"/>
+      <c r="I2137" t="n">
+        <v>23</v>
+      </c>
+      <c r="J2137" t="n">
+        <v>134</v>
+      </c>
+      <c r="K2137" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="L2137" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2138" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2138" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="F2138" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="G2138" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2138" t="inlineStr"/>
+      <c r="I2138" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2138" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2138" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="L2138" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2139" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2139" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="G2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2139" t="inlineStr"/>
+      <c r="I2139" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2139" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2139" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="L2139" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2140" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2140" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2140" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="F2140" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="G2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2140" t="inlineStr"/>
+      <c r="I2140" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J2140" t="n">
+        <v>101</v>
+      </c>
+      <c r="K2140" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="L2140" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2140"/>
+  <dimension ref="A1:L2145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89866,6 +89866,206 @@
         </is>
       </c>
     </row>
+    <row r="2141">
+      <c r="A2141" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2141" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2141" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2141" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="F2141" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="G2141" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2141" t="inlineStr"/>
+      <c r="I2141" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2141" t="n">
+        <v>191</v>
+      </c>
+      <c r="K2141" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="L2141" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2142" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2142" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2142" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F2142" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="G2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2142" t="inlineStr"/>
+      <c r="I2142" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2142" t="n">
+        <v>137</v>
+      </c>
+      <c r="K2142" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="L2142" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2143" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2143" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2143" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="F2143" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="G2143" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2143" t="inlineStr"/>
+      <c r="I2143" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2143" t="n">
+        <v>33</v>
+      </c>
+      <c r="K2143" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="L2143" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2144" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2144" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="F2144" t="n">
+        <v>63</v>
+      </c>
+      <c r="G2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2144" t="inlineStr"/>
+      <c r="I2144" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2144" t="n">
+        <v>86</v>
+      </c>
+      <c r="K2144" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="L2144" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2145" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2145" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2145" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F2145" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="G2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2145" t="inlineStr"/>
+      <c r="I2145" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2145" t="n">
+        <v>104</v>
+      </c>
+      <c r="K2145" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="L2145" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2145"/>
+  <dimension ref="A1:L2150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90066,6 +90066,206 @@
         </is>
       </c>
     </row>
+    <row r="2146">
+      <c r="A2146" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2146" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2146" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="F2146" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="G2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2146" t="inlineStr"/>
+      <c r="I2146" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2146" t="n">
+        <v>199</v>
+      </c>
+      <c r="K2146" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="L2146" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2147" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2147" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2147" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="F2147" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="G2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2147" t="inlineStr"/>
+      <c r="I2147" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2147" t="n">
+        <v>132</v>
+      </c>
+      <c r="K2147" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="L2147" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2148" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2148" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2148" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="F2148" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="G2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2148" t="inlineStr"/>
+      <c r="I2148" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2148" t="n">
+        <v>54</v>
+      </c>
+      <c r="K2148" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="L2148" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2149" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2149" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2149" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="F2149" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="G2149" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2149" t="inlineStr"/>
+      <c r="I2149" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2149" t="n">
+        <v>89</v>
+      </c>
+      <c r="K2149" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="L2149" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2150" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2150" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2150" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="F2150" t="n">
+        <v>64</v>
+      </c>
+      <c r="G2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2150" t="inlineStr"/>
+      <c r="I2150" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2150" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2150" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L2150" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2150"/>
+  <dimension ref="A1:L2155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90266,6 +90266,206 @@
         </is>
       </c>
     </row>
+    <row r="2151">
+      <c r="A2151" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2151" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2151" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2151" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="F2151" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="G2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2151" t="inlineStr"/>
+      <c r="I2151" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J2151" t="n">
+        <v>194</v>
+      </c>
+      <c r="K2151" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L2151" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2152" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2152" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2152" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F2152" t="n">
+        <v>73.67</v>
+      </c>
+      <c r="G2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2152" t="inlineStr"/>
+      <c r="I2152" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J2152" t="n">
+        <v>148</v>
+      </c>
+      <c r="K2152" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="L2152" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2153" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2153" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2153" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="F2153" t="n">
+        <v>68.70999999999999</v>
+      </c>
+      <c r="G2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2153" t="inlineStr"/>
+      <c r="I2153" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2153" t="n">
+        <v>54</v>
+      </c>
+      <c r="K2153" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2153" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2154" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2154" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2154" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="F2154" t="n">
+        <v>66.56999999999999</v>
+      </c>
+      <c r="G2154" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2154" t="inlineStr"/>
+      <c r="I2154" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J2154" t="n">
+        <v>97</v>
+      </c>
+      <c r="K2154" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="L2154" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2155" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2155" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2155" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="F2155" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2155" t="inlineStr"/>
+      <c r="I2155" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2155" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2155" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="L2155" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2155"/>
+  <dimension ref="A1:L2160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90466,6 +90466,206 @@
         </is>
       </c>
     </row>
+    <row r="2156">
+      <c r="A2156" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2156" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2156" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2156" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="F2156" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="G2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2156" t="inlineStr"/>
+      <c r="I2156" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J2156" t="n">
+        <v>194</v>
+      </c>
+      <c r="K2156" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="L2156" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2157" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2157" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2157" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="F2157" t="n">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="G2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2157" t="inlineStr"/>
+      <c r="I2157" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J2157" t="n">
+        <v>166</v>
+      </c>
+      <c r="K2157" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="L2157" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2158" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2158" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2158" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="F2158" t="n">
+        <v>72.76000000000001</v>
+      </c>
+      <c r="G2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2158" t="inlineStr"/>
+      <c r="I2158" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J2158" t="n">
+        <v>55</v>
+      </c>
+      <c r="K2158" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L2158" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2159" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2159" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2159" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="F2159" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="G2159" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2159" t="inlineStr"/>
+      <c r="I2159" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J2159" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2159" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="L2159" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2160" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2160" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2160" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F2160" t="n">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="G2160" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2160" t="inlineStr"/>
+      <c r="I2160" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2160" t="n">
+        <v>104</v>
+      </c>
+      <c r="K2160" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="L2160" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2160"/>
+  <dimension ref="A1:L2165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90666,6 +90666,206 @@
         </is>
       </c>
     </row>
+    <row r="2161">
+      <c r="A2161" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2161" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2161" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2161" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2161" t="n">
+        <v>73.76000000000001</v>
+      </c>
+      <c r="G2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2161" t="inlineStr"/>
+      <c r="I2161" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2161" t="n">
+        <v>192</v>
+      </c>
+      <c r="K2161" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="L2161" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2162" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2162" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2162" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F2162" t="n">
+        <v>78.67</v>
+      </c>
+      <c r="G2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2162" t="inlineStr"/>
+      <c r="I2162" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J2162" t="n">
+        <v>146</v>
+      </c>
+      <c r="K2162" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="L2162" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2163" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2163" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2163" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="F2163" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="G2163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2163" t="inlineStr"/>
+      <c r="I2163" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J2163" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2163" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L2163" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2164" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2164" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2164" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="F2164" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="G2164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2164" t="inlineStr"/>
+      <c r="I2164" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J2164" t="n">
+        <v>101</v>
+      </c>
+      <c r="K2164" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="L2164" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2165" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2165" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2165" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="F2165" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="G2165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2165" t="inlineStr"/>
+      <c r="I2165" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J2165" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2165" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="L2165" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2165"/>
+  <dimension ref="A1:L2170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90866,6 +90866,206 @@
         </is>
       </c>
     </row>
+    <row r="2166">
+      <c r="A2166" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2166" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2166" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2166" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="F2166" t="n">
+        <v>73.52</v>
+      </c>
+      <c r="G2166" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2166" t="inlineStr"/>
+      <c r="I2166" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J2166" t="n">
+        <v>189</v>
+      </c>
+      <c r="K2166" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="L2166" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2167" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2167" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2167" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F2167" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="G2167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2167" t="inlineStr"/>
+      <c r="I2167" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J2167" t="n">
+        <v>142</v>
+      </c>
+      <c r="K2167" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="L2167" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2168" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2168" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2168" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F2168" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="G2168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2168" t="inlineStr"/>
+      <c r="I2168" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2168" t="n">
+        <v>66</v>
+      </c>
+      <c r="K2168" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="L2168" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2169" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2169" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2169" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="F2169" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="G2169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2169" t="inlineStr"/>
+      <c r="I2169" t="n">
+        <v>17</v>
+      </c>
+      <c r="J2169" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2169" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="L2169" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2170" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2170" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2170" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F2170" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="G2170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2170" t="inlineStr"/>
+      <c r="I2170" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J2170" t="n">
+        <v>109</v>
+      </c>
+      <c r="K2170" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="L2170" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2170"/>
+  <dimension ref="A1:L2175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91066,6 +91066,206 @@
         </is>
       </c>
     </row>
+    <row r="2171">
+      <c r="A2171" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2171" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2171" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2171" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="F2171" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="G2171" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2171" t="inlineStr"/>
+      <c r="I2171" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="J2171" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2171" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="L2171" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2172" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2172" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2172" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="F2172" t="n">
+        <v>78</v>
+      </c>
+      <c r="G2172" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2172" t="inlineStr"/>
+      <c r="I2172" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J2172" t="n">
+        <v>147</v>
+      </c>
+      <c r="K2172" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L2172" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2173" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2173" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2173" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2173" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="G2173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2173" t="inlineStr"/>
+      <c r="I2173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J2173" t="n">
+        <v>69</v>
+      </c>
+      <c r="K2173" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L2173" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2174" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2174" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2174" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2174" t="n">
+        <v>71</v>
+      </c>
+      <c r="G2174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2174" t="inlineStr"/>
+      <c r="I2174" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J2174" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2174" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="L2174" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2175" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2175" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2175" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="F2175" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="G2175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2175" t="inlineStr"/>
+      <c r="I2175" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2175" t="n">
+        <v>109</v>
+      </c>
+      <c r="K2175" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="L2175" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2175"/>
+  <dimension ref="A1:L2180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91266,6 +91266,206 @@
         </is>
       </c>
     </row>
+    <row r="2176">
+      <c r="A2176" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2176" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2176" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2176" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="F2176" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="G2176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2176" t="inlineStr"/>
+      <c r="I2176" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2176" t="n">
+        <v>204</v>
+      </c>
+      <c r="K2176" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="L2176" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2177" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2177" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2177" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="F2177" t="n">
+        <v>80</v>
+      </c>
+      <c r="G2177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2177" t="inlineStr"/>
+      <c r="I2177" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J2177" t="n">
+        <v>142</v>
+      </c>
+      <c r="K2177" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="L2177" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2178" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2178" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2178" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="F2178" t="n">
+        <v>74.62</v>
+      </c>
+      <c r="G2178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2178" t="inlineStr"/>
+      <c r="I2178" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J2178" t="n">
+        <v>26</v>
+      </c>
+      <c r="K2178" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="L2178" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2179" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2179" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2179" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="F2179" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="G2179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2179" t="inlineStr"/>
+      <c r="I2179" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J2179" t="n">
+        <v>94</v>
+      </c>
+      <c r="K2179" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="L2179" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2180" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2180" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2180" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2180" t="n">
+        <v>66.48</v>
+      </c>
+      <c r="G2180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2180" t="inlineStr"/>
+      <c r="I2180" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2180" t="n">
+        <v>115</v>
+      </c>
+      <c r="K2180" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="L2180" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2180"/>
+  <dimension ref="A1:L2185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91466,6 +91466,206 @@
         </is>
       </c>
     </row>
+    <row r="2181">
+      <c r="A2181" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2181" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2181" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2181" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="F2181" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="G2181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2181" t="inlineStr"/>
+      <c r="I2181" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J2181" t="n">
+        <v>195</v>
+      </c>
+      <c r="K2181" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="L2181" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2182" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2182" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2182" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="F2182" t="n">
+        <v>79.48</v>
+      </c>
+      <c r="G2182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2182" t="inlineStr"/>
+      <c r="I2182" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2182" t="n">
+        <v>142</v>
+      </c>
+      <c r="K2182" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L2182" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2183" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2183" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2183" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2183" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="G2183" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2183" t="inlineStr"/>
+      <c r="I2183" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J2183" t="n">
+        <v>32</v>
+      </c>
+      <c r="K2183" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="L2183" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2184" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2184" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2184" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="F2184" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="G2184" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2184" t="inlineStr"/>
+      <c r="I2184" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2184" t="n">
+        <v>87</v>
+      </c>
+      <c r="K2184" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="L2184" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2185" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2185" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2185" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="F2185" t="n">
+        <v>65.38</v>
+      </c>
+      <c r="G2185" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2185" t="inlineStr"/>
+      <c r="I2185" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="J2185" t="n">
+        <v>99</v>
+      </c>
+      <c r="K2185" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="L2185" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2185"/>
+  <dimension ref="A1:L2190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91666,6 +91666,206 @@
         </is>
       </c>
     </row>
+    <row r="2186">
+      <c r="A2186" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2186" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2186" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2186" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="F2186" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="G2186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2186" t="inlineStr"/>
+      <c r="I2186" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J2186" t="n">
+        <v>121</v>
+      </c>
+      <c r="K2186" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="L2186" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2187" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2187" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2187" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F2187" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="G2187" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2187" t="inlineStr"/>
+      <c r="I2187" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J2187" t="n">
+        <v>119</v>
+      </c>
+      <c r="K2187" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="L2187" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2188" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2188" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2188" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="F2188" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="G2188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2188" t="inlineStr"/>
+      <c r="I2188" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="J2188" t="n">
+        <v>119</v>
+      </c>
+      <c r="K2188" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="L2188" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2189" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2189" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2189" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="F2189" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="G2189" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2189" t="inlineStr"/>
+      <c r="I2189" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2189" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2189" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="L2189" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2190" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2190" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2190" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="F2190" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="G2190" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2190" t="inlineStr"/>
+      <c r="I2190" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2190" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2190" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="L2190" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2190"/>
+  <dimension ref="A1:L2195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91866,6 +91866,206 @@
         </is>
       </c>
     </row>
+    <row r="2191">
+      <c r="A2191" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2191" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2191" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2191" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="F2191" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G2191" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2191" t="inlineStr"/>
+      <c r="I2191" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="J2191" t="n">
+        <v>189</v>
+      </c>
+      <c r="K2191" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="L2191" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2192" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2192" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2192" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="F2192" t="n">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="G2192" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2192" t="inlineStr"/>
+      <c r="I2192" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2192" t="n">
+        <v>129</v>
+      </c>
+      <c r="K2192" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="L2192" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2193" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2193" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2193" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2193" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="G2193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2193" t="inlineStr"/>
+      <c r="I2193" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2193" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2193" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="L2193" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2194" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2194" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2194" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F2194" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="G2194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2194" t="inlineStr"/>
+      <c r="I2194" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2194" t="n">
+        <v>113</v>
+      </c>
+      <c r="K2194" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="L2194" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2195" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2195" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2195" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="F2195" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G2195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2195" t="inlineStr"/>
+      <c r="I2195" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2195" t="n">
+        <v>103</v>
+      </c>
+      <c r="K2195" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="L2195" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2195"/>
+  <dimension ref="A1:L2200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92066,6 +92066,206 @@
         </is>
       </c>
     </row>
+    <row r="2196">
+      <c r="A2196" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2196" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2196" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2196" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="F2196" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="G2196" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2196" t="inlineStr"/>
+      <c r="I2196" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J2196" t="n">
+        <v>192</v>
+      </c>
+      <c r="K2196" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="L2196" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2197" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2197" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2197" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F2197" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="G2197" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2197" t="inlineStr"/>
+      <c r="I2197" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2197" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2197" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="L2197" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2198" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2198" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2198" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="F2198" t="n">
+        <v>78.19</v>
+      </c>
+      <c r="G2198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2198" t="inlineStr"/>
+      <c r="I2198" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2198" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2198" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="L2198" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2199" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2199" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2199" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="F2199" t="n">
+        <v>67</v>
+      </c>
+      <c r="G2199" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2199" t="inlineStr"/>
+      <c r="I2199" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2199" t="n">
+        <v>157</v>
+      </c>
+      <c r="K2199" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="L2199" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2200" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2200" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2200" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="F2200" t="n">
+        <v>65</v>
+      </c>
+      <c r="G2200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2200" t="inlineStr"/>
+      <c r="I2200" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2200" t="n">
+        <v>157</v>
+      </c>
+      <c r="K2200" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="L2200" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2200"/>
+  <dimension ref="A1:L2205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92266,6 +92266,206 @@
         </is>
       </c>
     </row>
+    <row r="2201">
+      <c r="A2201" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2201" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2201" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2201" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="F2201" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="G2201" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2201" t="inlineStr"/>
+      <c r="I2201" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="J2201" t="n">
+        <v>130</v>
+      </c>
+      <c r="K2201" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L2201" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2202" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2202" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2202" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="F2202" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="G2202" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2202" t="inlineStr"/>
+      <c r="I2202" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J2202" t="n">
+        <v>126</v>
+      </c>
+      <c r="K2202" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="L2202" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2203" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2203" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2203" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="F2203" t="n">
+        <v>76.62</v>
+      </c>
+      <c r="G2203" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2203" t="inlineStr"/>
+      <c r="I2203" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2203" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2203" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="L2203" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2204" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2204" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2204" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="F2204" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="G2204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2204" t="inlineStr"/>
+      <c r="I2204" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2204" t="n">
+        <v>118</v>
+      </c>
+      <c r="K2204" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="L2204" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2205" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2205" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2205" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2205" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="G2205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2205" t="inlineStr"/>
+      <c r="I2205" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2205" t="n">
+        <v>119</v>
+      </c>
+      <c r="K2205" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="L2205" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2205"/>
+  <dimension ref="A1:L2210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92466,6 +92466,206 @@
         </is>
       </c>
     </row>
+    <row r="2206">
+      <c r="A2206" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2206" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2206" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2206" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="F2206" t="n">
+        <v>68</v>
+      </c>
+      <c r="G2206" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2206" t="inlineStr"/>
+      <c r="I2206" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J2206" t="n">
+        <v>114</v>
+      </c>
+      <c r="K2206" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="L2206" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2207" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2207" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2207" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="F2207" t="n">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="G2207" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2207" t="inlineStr"/>
+      <c r="I2207" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J2207" t="n">
+        <v>121</v>
+      </c>
+      <c r="K2207" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="L2207" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2208" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2208" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2208" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="F2208" t="n">
+        <v>72.48</v>
+      </c>
+      <c r="G2208" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2208" t="inlineStr"/>
+      <c r="I2208" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2208" t="n">
+        <v>108</v>
+      </c>
+      <c r="K2208" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="L2208" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2209" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2209" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2209" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="F2209" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="G2209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2209" t="inlineStr"/>
+      <c r="I2209" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="J2209" t="n">
+        <v>115</v>
+      </c>
+      <c r="K2209" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="L2209" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2210" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2210" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2210" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F2210" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="G2210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2210" t="inlineStr"/>
+      <c r="I2210" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2210" t="n">
+        <v>110</v>
+      </c>
+      <c r="K2210" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="L2210" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2210"/>
+  <dimension ref="A1:L2215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92666,6 +92666,206 @@
         </is>
       </c>
     </row>
+    <row r="2211">
+      <c r="A2211" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2211" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2211" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2211" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="F2211" t="n">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="G2211" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2211" t="inlineStr"/>
+      <c r="I2211" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2211" t="n">
+        <v>181</v>
+      </c>
+      <c r="K2211" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L2211" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2212" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2212" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2212" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="F2212" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="G2212" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2212" t="inlineStr"/>
+      <c r="I2212" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2212" t="n">
+        <v>140</v>
+      </c>
+      <c r="K2212" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="L2212" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2213" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2213" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2213" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="F2213" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="G2213" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2213" t="inlineStr"/>
+      <c r="I2213" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2213" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2213" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="L2213" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2214" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2214" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2214" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F2214" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G2214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2214" t="inlineStr"/>
+      <c r="I2214" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2214" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2214" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="L2214" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2215" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2215" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2215" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="F2215" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="G2215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2215" t="inlineStr"/>
+      <c r="I2215" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2215" t="n">
+        <v>42</v>
+      </c>
+      <c r="K2215" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="L2215" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2215"/>
+  <dimension ref="A1:L2220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92866,6 +92866,206 @@
         </is>
       </c>
     </row>
+    <row r="2216">
+      <c r="A2216" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2216" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2216" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2216" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="F2216" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="G2216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2216" t="inlineStr"/>
+      <c r="I2216" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="J2216" t="n">
+        <v>197</v>
+      </c>
+      <c r="K2216" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="L2216" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2217" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2217" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2217" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2217" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="G2217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2217" t="inlineStr"/>
+      <c r="I2217" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J2217" t="n">
+        <v>133</v>
+      </c>
+      <c r="K2217" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="L2217" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2218" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2218" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2218" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F2218" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="G2218" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2218" t="inlineStr"/>
+      <c r="I2218" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J2218" t="n">
+        <v>236</v>
+      </c>
+      <c r="K2218" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="L2218" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2219" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2219" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2219" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="F2219" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="G2219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2219" t="inlineStr"/>
+      <c r="I2219" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J2219" t="n">
+        <v>84</v>
+      </c>
+      <c r="K2219" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="L2219" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2220" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2220" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2220" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="F2220" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="G2220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2220" t="inlineStr"/>
+      <c r="I2220" t="n">
+        <v>18</v>
+      </c>
+      <c r="J2220" t="n">
+        <v>88</v>
+      </c>
+      <c r="K2220" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L2220" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2220"/>
+  <dimension ref="A1:L2225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93066,6 +93066,206 @@
         </is>
       </c>
     </row>
+    <row r="2221">
+      <c r="A2221" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2221" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2221" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2221" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2221" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="G2221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2221" t="inlineStr"/>
+      <c r="I2221" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J2221" t="n">
+        <v>190</v>
+      </c>
+      <c r="K2221" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="L2221" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2222" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2222" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2222" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F2222" t="n">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="G2222" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2222" t="inlineStr"/>
+      <c r="I2222" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2222" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2222" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="L2222" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2223" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2223" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2223" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="F2223" t="n">
+        <v>63.52</v>
+      </c>
+      <c r="G2223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2223" t="inlineStr"/>
+      <c r="I2223" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2223" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2223" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="L2223" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2224" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2224" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2224" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="F2224" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="G2224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2224" t="inlineStr"/>
+      <c r="I2224" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2224" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2224" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="L2224" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2225" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2225" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2225" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F2225" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="G2225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2225" t="inlineStr"/>
+      <c r="I2225" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2225" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2225" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="L2225" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2225"/>
+  <dimension ref="A1:L2230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93266,6 +93266,206 @@
         </is>
       </c>
     </row>
+    <row r="2226">
+      <c r="A2226" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2226" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2226" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2226" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="F2226" t="n">
+        <v>69.62</v>
+      </c>
+      <c r="G2226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2226" t="inlineStr"/>
+      <c r="I2226" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2226" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2226" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="L2226" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2227" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2227" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2227" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="G2227" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2227" t="inlineStr"/>
+      <c r="I2227" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2227" t="n">
+        <v>158</v>
+      </c>
+      <c r="K2227" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="L2227" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2228" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2228" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2228" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="F2228" t="n">
+        <v>71.81</v>
+      </c>
+      <c r="G2228" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2228" t="inlineStr"/>
+      <c r="I2228" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2228" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2228" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="L2228" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2229" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2229" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2229" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F2229" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="G2229" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2229" t="inlineStr"/>
+      <c r="I2229" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2229" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2229" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="L2229" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2230" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2230" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2230" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2230" t="n">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="G2230" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2230" t="inlineStr"/>
+      <c r="I2230" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2230" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2230" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L2230" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2230"/>
+  <dimension ref="A1:L2235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93466,6 +93466,206 @@
         </is>
       </c>
     </row>
+    <row r="2231">
+      <c r="A2231" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2231" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2231" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2231" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="F2231" t="n">
+        <v>71.48</v>
+      </c>
+      <c r="G2231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2231" t="inlineStr"/>
+      <c r="I2231" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J2231" t="n">
+        <v>203</v>
+      </c>
+      <c r="K2231" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="L2231" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2232" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2232" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="G2232" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2232" t="inlineStr"/>
+      <c r="I2232" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J2232" t="n">
+        <v>132</v>
+      </c>
+      <c r="K2232" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="L2232" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2233" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2233" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2233" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="F2233" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="G2233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2233" t="inlineStr"/>
+      <c r="I2233" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J2233" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2233" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="L2233" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2234" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2234" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2234" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="F2234" t="n">
+        <v>69.56999999999999</v>
+      </c>
+      <c r="G2234" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2234" t="inlineStr"/>
+      <c r="I2234" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="J2234" t="n">
+        <v>87</v>
+      </c>
+      <c r="K2234" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="L2234" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2235" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2235" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2235" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F2235" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="G2235" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2235" t="inlineStr"/>
+      <c r="I2235" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="J2235" t="n">
+        <v>108</v>
+      </c>
+      <c r="K2235" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="L2235" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2235"/>
+  <dimension ref="A1:L2240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93666,6 +93666,206 @@
         </is>
       </c>
     </row>
+    <row r="2236">
+      <c r="A2236" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2236" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2236" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2236" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="F2236" t="n">
+        <v>73.76000000000001</v>
+      </c>
+      <c r="G2236" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2236" t="inlineStr"/>
+      <c r="I2236" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2236" t="n">
+        <v>183</v>
+      </c>
+      <c r="K2236" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="L2236" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2237" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2237" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="G2237" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2237" t="inlineStr"/>
+      <c r="I2237" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2237" t="n">
+        <v>124</v>
+      </c>
+      <c r="K2237" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="L2237" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2238" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2238" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2238" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="F2238" t="n">
+        <v>78.76000000000001</v>
+      </c>
+      <c r="G2238" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2238" t="inlineStr"/>
+      <c r="I2238" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2238" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2238" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L2238" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2239" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2239" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2239" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="F2239" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="G2239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2239" t="inlineStr"/>
+      <c r="I2239" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2239" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2239" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="L2239" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2240" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2240" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>69.43000000000001</v>
+      </c>
+      <c r="G2240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2240" t="inlineStr"/>
+      <c r="I2240" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2240" t="n">
+        <v>115</v>
+      </c>
+      <c r="K2240" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="L2240" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2240"/>
+  <dimension ref="A1:L2245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93866,6 +93866,206 @@
         </is>
       </c>
     </row>
+    <row r="2241">
+      <c r="A2241" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2241" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2241" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2241" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="F2241" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="G2241" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2241" t="inlineStr"/>
+      <c r="I2241" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J2241" t="n">
+        <v>199</v>
+      </c>
+      <c r="K2241" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="L2241" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2242" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2242" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2242" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F2242" t="n">
+        <v>82.70999999999999</v>
+      </c>
+      <c r="G2242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2242" t="inlineStr"/>
+      <c r="I2242" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J2242" t="n">
+        <v>148</v>
+      </c>
+      <c r="K2242" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="L2242" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2243" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2243" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="G2243" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H2243" t="inlineStr"/>
+      <c r="I2243" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J2243" t="n">
+        <v>37</v>
+      </c>
+      <c r="K2243" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="L2243" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2244" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2244" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="G2244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2244" t="inlineStr"/>
+      <c r="I2244" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2244" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2244" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="L2244" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2245" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2245" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2245" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="F2245" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G2245" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2245" t="inlineStr"/>
+      <c r="I2245" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J2245" t="n">
+        <v>108</v>
+      </c>
+      <c r="K2245" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L2245" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2245"/>
+  <dimension ref="A1:L2250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94066,6 +94066,206 @@
         </is>
       </c>
     </row>
+    <row r="2246">
+      <c r="A2246" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2246" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2246" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>72.56999999999999</v>
+      </c>
+      <c r="G2246" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2246" t="inlineStr"/>
+      <c r="I2246" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J2246" t="n">
+        <v>191</v>
+      </c>
+      <c r="K2246" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="L2246" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2247" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2247" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2247" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F2247" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="G2247" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2247" t="inlineStr"/>
+      <c r="I2247" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J2247" t="n">
+        <v>146</v>
+      </c>
+      <c r="K2247" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="L2247" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2248" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2248" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2248" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="F2248" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="G2248" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H2248" t="inlineStr"/>
+      <c r="I2248" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2248" t="n">
+        <v>49</v>
+      </c>
+      <c r="K2248" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="L2248" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2249" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2249" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2249" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F2249" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="G2249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2249" t="inlineStr"/>
+      <c r="I2249" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J2249" t="n">
+        <v>99</v>
+      </c>
+      <c r="K2249" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L2249" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2250" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2250" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2250" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="F2250" t="n">
+        <v>67.62</v>
+      </c>
+      <c r="G2250" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2250" t="inlineStr"/>
+      <c r="I2250" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J2250" t="n">
+        <v>110</v>
+      </c>
+      <c r="K2250" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="L2250" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2250"/>
+  <dimension ref="A1:L2255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94266,6 +94266,206 @@
         </is>
       </c>
     </row>
+    <row r="2251">
+      <c r="A2251" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2251" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2251" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2251" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="F2251" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="G2251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2251" t="inlineStr"/>
+      <c r="I2251" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2251" t="n">
+        <v>188</v>
+      </c>
+      <c r="K2251" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="L2251" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2252" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2252" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2252" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="F2252" t="n">
+        <v>82.14</v>
+      </c>
+      <c r="G2252" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2252" t="inlineStr"/>
+      <c r="I2252" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J2252" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2252" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="L2252" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2253" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2253" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2253" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2253" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="G2253" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2253" t="inlineStr"/>
+      <c r="I2253" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2253" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2253" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L2253" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2254" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2254" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2254" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="F2254" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="G2254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2254" t="inlineStr"/>
+      <c r="I2254" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J2254" t="n">
+        <v>94</v>
+      </c>
+      <c r="K2254" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="L2254" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2255" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2255" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2255" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="F2255" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="G2255" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2255" t="inlineStr"/>
+      <c r="I2255" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2255" t="n">
+        <v>110</v>
+      </c>
+      <c r="K2255" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="L2255" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2255"/>
+  <dimension ref="A1:L2260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94466,6 +94466,206 @@
         </is>
       </c>
     </row>
+    <row r="2256">
+      <c r="A2256" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2256" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2256" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2256" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="F2256" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="G2256" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2256" t="inlineStr"/>
+      <c r="I2256" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2256" t="n">
+        <v>189</v>
+      </c>
+      <c r="K2256" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="L2256" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2257" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2257" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2257" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="F2257" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="G2257" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2257" t="inlineStr"/>
+      <c r="I2257" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2257" t="n">
+        <v>136</v>
+      </c>
+      <c r="K2257" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="L2257" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2258" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2258" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2258" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2258" t="n">
+        <v>80.23999999999999</v>
+      </c>
+      <c r="G2258" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2258" t="inlineStr"/>
+      <c r="I2258" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2258" t="n">
+        <v>132</v>
+      </c>
+      <c r="K2258" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="L2258" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2259" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2259" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2259" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F2259" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="G2259" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2259" t="inlineStr"/>
+      <c r="I2259" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="J2259" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2259" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="L2259" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2260" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2260" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2260" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="F2260" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="G2260" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H2260" t="inlineStr"/>
+      <c r="I2260" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J2260" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2260" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="L2260" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2260"/>
+  <dimension ref="A1:L2265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94666,6 +94666,206 @@
         </is>
       </c>
     </row>
+    <row r="2261">
+      <c r="A2261" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2261" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2261" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2261" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="F2261" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="G2261" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2261" t="inlineStr"/>
+      <c r="I2261" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J2261" t="n">
+        <v>175</v>
+      </c>
+      <c r="K2261" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L2261" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2262" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2262" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2262" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="F2262" t="n">
+        <v>81.29000000000001</v>
+      </c>
+      <c r="G2262" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2262" t="inlineStr"/>
+      <c r="I2262" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J2262" t="n">
+        <v>179</v>
+      </c>
+      <c r="K2262" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="L2262" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2263" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2263" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2263" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2263" t="n">
+        <v>80.23999999999999</v>
+      </c>
+      <c r="G2263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2263" t="inlineStr"/>
+      <c r="I2263" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2263" t="n">
+        <v>114</v>
+      </c>
+      <c r="K2263" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="L2263" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2264" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2264" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2264" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="F2264" t="n">
+        <v>73.76000000000001</v>
+      </c>
+      <c r="G2264" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2264" t="inlineStr"/>
+      <c r="I2264" t="n">
+        <v>21</v>
+      </c>
+      <c r="J2264" t="n">
+        <v>99</v>
+      </c>
+      <c r="K2264" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="L2264" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2265" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2265" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2265" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="F2265" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="G2265" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2265" t="inlineStr"/>
+      <c r="I2265" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J2265" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2265" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="L2265" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2265"/>
+  <dimension ref="A1:L2270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94866,6 +94866,206 @@
         </is>
       </c>
     </row>
+    <row r="2266">
+      <c r="A2266" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2266" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2266" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2266" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="F2266" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="G2266" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2266" t="inlineStr"/>
+      <c r="I2266" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J2266" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2266" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="L2266" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2267" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2267" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2267" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="F2267" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="G2267" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2267" t="inlineStr"/>
+      <c r="I2267" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2267" t="n">
+        <v>118</v>
+      </c>
+      <c r="K2267" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L2267" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2268" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2268" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2268" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="F2268" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="G2268" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2268" t="inlineStr"/>
+      <c r="I2268" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2268" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2268" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="L2268" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2269" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2269" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2269" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2269" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="G2269" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2269" t="inlineStr"/>
+      <c r="I2269" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="J2269" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2269" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="L2269" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2270" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2270" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2270" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2270" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="G2270" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2270" t="inlineStr"/>
+      <c r="I2270" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="J2270" t="n">
+        <v>115</v>
+      </c>
+      <c r="K2270" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="L2270" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2270"/>
+  <dimension ref="A1:L2275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95066,6 +95066,206 @@
         </is>
       </c>
     </row>
+    <row r="2271">
+      <c r="A2271" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2271" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2271" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2271" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="F2271" t="n">
+        <v>71.86</v>
+      </c>
+      <c r="G2271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2271" t="inlineStr"/>
+      <c r="I2271" t="n">
+        <v>21</v>
+      </c>
+      <c r="J2271" t="n">
+        <v>191</v>
+      </c>
+      <c r="K2271" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="L2271" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2272" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2272" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2272" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F2272" t="n">
+        <v>80.19</v>
+      </c>
+      <c r="G2272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2272" t="inlineStr"/>
+      <c r="I2272" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J2272" t="n">
+        <v>147</v>
+      </c>
+      <c r="K2272" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L2272" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2273" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2273" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2273" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="F2273" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="G2273" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2273" t="inlineStr"/>
+      <c r="I2273" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J2273" t="n">
+        <v>38</v>
+      </c>
+      <c r="K2273" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="L2273" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2274" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2274" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2274" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="F2274" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="G2274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2274" t="inlineStr"/>
+      <c r="I2274" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J2274" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2274" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="L2274" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2275" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2275" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2275" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F2275" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="G2275" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2275" t="inlineStr"/>
+      <c r="I2275" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J2275" t="n">
+        <v>115</v>
+      </c>
+      <c r="K2275" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="L2275" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2275"/>
+  <dimension ref="A1:L2280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95266,6 +95266,206 @@
         </is>
       </c>
     </row>
+    <row r="2276">
+      <c r="A2276" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2276" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2276" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2276" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="F2276" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="G2276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2276" t="inlineStr"/>
+      <c r="I2276" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J2276" t="n">
+        <v>218</v>
+      </c>
+      <c r="K2276" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="L2276" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2277" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2277" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="G2277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2277" t="inlineStr"/>
+      <c r="I2277" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J2277" t="n">
+        <v>167</v>
+      </c>
+      <c r="K2277" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="L2277" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2278" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2278" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2278" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="F2278" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="G2278" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2278" t="inlineStr"/>
+      <c r="I2278" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J2278" t="n">
+        <v>41</v>
+      </c>
+      <c r="K2278" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="L2278" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2279" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2279" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F2279" t="n">
+        <v>68.70999999999999</v>
+      </c>
+      <c r="G2279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2279" t="inlineStr"/>
+      <c r="I2279" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J2279" t="n">
+        <v>80</v>
+      </c>
+      <c r="K2279" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="L2279" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2280" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="G2280" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2280" t="inlineStr"/>
+      <c r="I2280" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J2280" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2280" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="L2280" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2280"/>
+  <dimension ref="A1:L2285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95466,6 +95466,206 @@
         </is>
       </c>
     </row>
+    <row r="2281">
+      <c r="A2281" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2281" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2281" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2281" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="F2281" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G2281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2281" t="inlineStr"/>
+      <c r="I2281" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2281" t="n">
+        <v>197</v>
+      </c>
+      <c r="K2281" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="L2281" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2282" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2282" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2282" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2282" t="n">
+        <v>78.43000000000001</v>
+      </c>
+      <c r="G2282" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2282" t="inlineStr"/>
+      <c r="I2282" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2282" t="n">
+        <v>162</v>
+      </c>
+      <c r="K2282" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="L2282" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2283" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2283" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>74.70999999999999</v>
+      </c>
+      <c r="G2283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2283" t="inlineStr"/>
+      <c r="I2283" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2283" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2283" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L2283" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2284" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2284" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2284" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="F2284" t="n">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="G2284" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2284" t="inlineStr"/>
+      <c r="I2284" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2284" t="n">
+        <v>76</v>
+      </c>
+      <c r="K2284" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="L2284" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2285" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="G2285" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2285" t="inlineStr"/>
+      <c r="I2285" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2285" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2285" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="L2285" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2285"/>
+  <dimension ref="A1:L2290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95666,6 +95666,206 @@
         </is>
       </c>
     </row>
+    <row r="2286">
+      <c r="A2286" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2286" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2286" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2286" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="F2286" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="G2286" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2286" t="inlineStr"/>
+      <c r="I2286" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2286" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2286" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="L2286" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2287" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2287" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2287" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F2287" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="G2287" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2287" t="inlineStr"/>
+      <c r="I2287" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2287" t="n">
+        <v>160</v>
+      </c>
+      <c r="K2287" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="L2287" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2288" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2288" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2288" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="F2288" t="n">
+        <v>74.05</v>
+      </c>
+      <c r="G2288" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2288" t="inlineStr"/>
+      <c r="I2288" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2288" t="n">
+        <v>55</v>
+      </c>
+      <c r="K2288" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="L2288" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2289" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2289" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="F2289" t="n">
+        <v>67.67</v>
+      </c>
+      <c r="G2289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2289" t="inlineStr"/>
+      <c r="I2289" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2289" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2289" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="L2289" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2290" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2290" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2290" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="F2290" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="G2290" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2290" t="inlineStr"/>
+      <c r="I2290" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2290" t="n">
+        <v>114</v>
+      </c>
+      <c r="K2290" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="L2290" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2290"/>
+  <dimension ref="A1:L2295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95866,6 +95866,206 @@
         </is>
       </c>
     </row>
+    <row r="2291">
+      <c r="A2291" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2291" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2291" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2291" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="F2291" t="n">
+        <v>69.38</v>
+      </c>
+      <c r="G2291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2291" t="inlineStr"/>
+      <c r="I2291" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J2291" t="n">
+        <v>192</v>
+      </c>
+      <c r="K2291" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2291" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2292" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2292" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2292" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2292" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="G2292" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2292" t="inlineStr"/>
+      <c r="I2292" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J2292" t="n">
+        <v>158</v>
+      </c>
+      <c r="K2292" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="L2292" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2293" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="G2293" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2293" t="inlineStr"/>
+      <c r="I2293" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2293" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2293" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="L2293" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2294" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G2294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2294" t="inlineStr"/>
+      <c r="I2294" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J2294" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2294" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L2294" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2295" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2295" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="F2295" t="n">
+        <v>62.43</v>
+      </c>
+      <c r="G2295" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2295" t="inlineStr"/>
+      <c r="I2295" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2295" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2295" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L2295" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2295"/>
+  <dimension ref="A1:L2300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96066,6 +96066,206 @@
         </is>
       </c>
     </row>
+    <row r="2296">
+      <c r="A2296" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2296" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2296" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="F2296" t="n">
+        <v>69.76000000000001</v>
+      </c>
+      <c r="G2296" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2296" t="inlineStr"/>
+      <c r="I2296" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J2296" t="n">
+        <v>185</v>
+      </c>
+      <c r="K2296" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="L2296" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2297" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>79.38</v>
+      </c>
+      <c r="G2297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2297" t="inlineStr"/>
+      <c r="I2297" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2297" t="n">
+        <v>153</v>
+      </c>
+      <c r="K2297" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="L2297" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2298" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="G2298" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2298" t="inlineStr"/>
+      <c r="I2298" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J2298" t="n">
+        <v>34</v>
+      </c>
+      <c r="K2298" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="L2298" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2299" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="G2299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2299" t="inlineStr"/>
+      <c r="I2299" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J2299" t="n">
+        <v>103</v>
+      </c>
+      <c r="K2299" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="L2299" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2300" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2300" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G2300" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2300" t="inlineStr"/>
+      <c r="I2300" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J2300" t="n">
+        <v>94</v>
+      </c>
+      <c r="K2300" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="L2300" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2300"/>
+  <dimension ref="A1:L2305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96266,6 +96266,206 @@
         </is>
       </c>
     </row>
+    <row r="2301">
+      <c r="A2301" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2301" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="G2301" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2301" t="inlineStr"/>
+      <c r="I2301" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J2301" t="n">
+        <v>193</v>
+      </c>
+      <c r="K2301" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="L2301" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2302" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2302" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="G2302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2302" t="inlineStr"/>
+      <c r="I2302" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J2302" t="n">
+        <v>165</v>
+      </c>
+      <c r="K2302" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="L2302" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2303" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2303" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>73.52</v>
+      </c>
+      <c r="G2303" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2303" t="inlineStr"/>
+      <c r="I2303" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2303" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2303" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="L2303" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2304" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2304" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2304" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="F2304" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="G2304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2304" t="inlineStr"/>
+      <c r="I2304" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J2304" t="n">
+        <v>104</v>
+      </c>
+      <c r="K2304" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="L2304" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2305" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2305" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2305" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F2305" t="n">
+        <v>60.57</v>
+      </c>
+      <c r="G2305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2305" t="inlineStr"/>
+      <c r="I2305" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J2305" t="n">
+        <v>97</v>
+      </c>
+      <c r="K2305" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="L2305" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2305"/>
+  <dimension ref="A1:L2310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96466,6 +96466,206 @@
         </is>
       </c>
     </row>
+    <row r="2306">
+      <c r="A2306" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2306" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2306" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2306" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="F2306" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="G2306" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2306" t="inlineStr"/>
+      <c r="I2306" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2306" t="n">
+        <v>183</v>
+      </c>
+      <c r="K2306" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="L2306" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2307" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>78.52</v>
+      </c>
+      <c r="G2307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2307" t="inlineStr"/>
+      <c r="I2307" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2307" t="n">
+        <v>156</v>
+      </c>
+      <c r="K2307" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="L2307" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2308" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2308" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2308" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="F2308" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="G2308" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2308" t="inlineStr"/>
+      <c r="I2308" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2308" t="n">
+        <v>33</v>
+      </c>
+      <c r="K2308" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="L2308" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2309" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2309" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2309" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="F2309" t="n">
+        <v>65.43000000000001</v>
+      </c>
+      <c r="G2309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2309" t="inlineStr"/>
+      <c r="I2309" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2309" t="n">
+        <v>84</v>
+      </c>
+      <c r="K2309" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="L2309" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2310" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2310" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2310" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F2310" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="G2310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2310" t="inlineStr"/>
+      <c r="I2310" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2310" t="n">
+        <v>97</v>
+      </c>
+      <c r="K2310" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="L2310" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2310"/>
+  <dimension ref="A1:L2315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96666,6 +96666,206 @@
         </is>
       </c>
     </row>
+    <row r="2311">
+      <c r="A2311" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2311" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2311" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2311" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="F2311" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="G2311" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2311" t="inlineStr"/>
+      <c r="I2311" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J2311" t="n">
+        <v>192</v>
+      </c>
+      <c r="K2311" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="L2311" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2312" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2312" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2312" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="F2312" t="n">
+        <v>78.81</v>
+      </c>
+      <c r="G2312" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2312" t="inlineStr"/>
+      <c r="I2312" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2312" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2312" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="L2312" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2313" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2313" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2313" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="F2313" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="G2313" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2313" t="inlineStr"/>
+      <c r="I2313" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2313" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2313" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="L2313" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2314" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2314" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2314" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="F2314" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G2314" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2314" t="inlineStr"/>
+      <c r="I2314" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2314" t="n">
+        <v>67</v>
+      </c>
+      <c r="K2314" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="L2314" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2315" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2315" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2315" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="G2315" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2315" t="inlineStr"/>
+      <c r="I2315" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2315" t="n">
+        <v>67</v>
+      </c>
+      <c r="K2315" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L2315" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2315"/>
+  <dimension ref="A1:L2320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96866,6 +96866,206 @@
         </is>
       </c>
     </row>
+    <row r="2316">
+      <c r="A2316" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2316" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2316" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2316" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="F2316" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="G2316" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2316" t="inlineStr"/>
+      <c r="I2316" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J2316" t="n">
+        <v>190</v>
+      </c>
+      <c r="K2316" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="L2316" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2317" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2317" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2317" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="F2317" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="G2317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2317" t="inlineStr"/>
+      <c r="I2317" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J2317" t="n">
+        <v>160</v>
+      </c>
+      <c r="K2317" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="L2317" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2318" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2318" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2318" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="F2318" t="n">
+        <v>74.52</v>
+      </c>
+      <c r="G2318" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2318" t="inlineStr"/>
+      <c r="I2318" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2318" t="n">
+        <v>35</v>
+      </c>
+      <c r="K2318" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L2318" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2319" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2319" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2319" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="F2319" t="n">
+        <v>67.81</v>
+      </c>
+      <c r="G2319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2319" t="inlineStr"/>
+      <c r="I2319" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="J2319" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2319" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="L2319" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2320" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2320" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2320" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="F2320" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="G2320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2320" t="inlineStr"/>
+      <c r="I2320" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J2320" t="n">
+        <v>94</v>
+      </c>
+      <c r="K2320" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="L2320" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2320"/>
+  <dimension ref="A1:L2325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97066,6 +97066,206 @@
         </is>
       </c>
     </row>
+    <row r="2321">
+      <c r="A2321" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2321" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2321" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2321" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F2321" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="G2321" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2321" t="inlineStr"/>
+      <c r="I2321" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2321" t="n">
+        <v>183</v>
+      </c>
+      <c r="K2321" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="L2321" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2322" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2322" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2322" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="F2322" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="G2322" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2322" t="inlineStr"/>
+      <c r="I2322" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2322" t="n">
+        <v>140</v>
+      </c>
+      <c r="K2322" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="L2322" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2323" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2323" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2323" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F2323" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="G2323" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2323" t="inlineStr"/>
+      <c r="I2323" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2323" t="n">
+        <v>127</v>
+      </c>
+      <c r="K2323" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L2323" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2324" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2324" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2324" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="F2324" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="G2324" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2324" t="inlineStr"/>
+      <c r="I2324" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J2324" t="n">
+        <v>109</v>
+      </c>
+      <c r="K2324" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="L2324" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2325" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="G2325" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2325" t="inlineStr"/>
+      <c r="I2325" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2325" t="n">
+        <v>109</v>
+      </c>
+      <c r="K2325" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L2325" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2325"/>
+  <dimension ref="A1:L2330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97266,6 +97266,206 @@
         </is>
       </c>
     </row>
+    <row r="2326">
+      <c r="A2326" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2326" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2326" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2326" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="F2326" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="G2326" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2326" t="inlineStr"/>
+      <c r="I2326" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J2326" t="n">
+        <v>188</v>
+      </c>
+      <c r="K2326" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="L2326" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2327" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2327" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="F2327" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="G2327" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2327" t="inlineStr"/>
+      <c r="I2327" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J2327" t="n">
+        <v>171</v>
+      </c>
+      <c r="K2327" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="L2327" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2328" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2328" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2328" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="F2328" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="G2328" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2328" t="inlineStr"/>
+      <c r="I2328" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J2328" t="n">
+        <v>48</v>
+      </c>
+      <c r="K2328" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="L2328" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2329" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2329" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F2329" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="G2329" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2329" t="inlineStr"/>
+      <c r="I2329" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J2329" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2329" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="L2329" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2330" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="F2330" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="G2330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2330" t="inlineStr"/>
+      <c r="I2330" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J2330" t="n">
+        <v>94</v>
+      </c>
+      <c r="K2330" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="L2330" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2330"/>
+  <dimension ref="A1:L2335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97466,6 +97466,206 @@
         </is>
       </c>
     </row>
+    <row r="2331">
+      <c r="A2331" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2331" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2331" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2331" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="F2331" t="n">
+        <v>74.70999999999999</v>
+      </c>
+      <c r="G2331" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2331" t="inlineStr"/>
+      <c r="I2331" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2331" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2331" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="L2331" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2332" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2332" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2332" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="F2332" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="G2332" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2332" t="inlineStr"/>
+      <c r="I2332" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2332" t="n">
+        <v>201</v>
+      </c>
+      <c r="K2332" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="L2332" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2333" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2333" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2333" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="F2333" t="n">
+        <v>78.76000000000001</v>
+      </c>
+      <c r="G2333" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2333" t="inlineStr"/>
+      <c r="I2333" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2333" t="n">
+        <v>51</v>
+      </c>
+      <c r="K2333" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="L2333" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2334" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2334" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2334" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="F2334" t="n">
+        <v>70</v>
+      </c>
+      <c r="G2334" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2334" t="inlineStr"/>
+      <c r="I2334" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2334" t="n">
+        <v>102</v>
+      </c>
+      <c r="K2334" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="L2334" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2335" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2335" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="F2335" t="n">
+        <v>66.56999999999999</v>
+      </c>
+      <c r="G2335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2335" t="inlineStr"/>
+      <c r="I2335" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2335" t="n">
+        <v>108</v>
+      </c>
+      <c r="K2335" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="L2335" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2335"/>
+  <dimension ref="A1:L2340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97666,6 +97666,206 @@
         </is>
       </c>
     </row>
+    <row r="2336">
+      <c r="A2336" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2336" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2336" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2336" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="F2336" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="G2336" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2336" t="inlineStr"/>
+      <c r="I2336" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J2336" t="n">
+        <v>187</v>
+      </c>
+      <c r="K2336" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="L2336" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2337" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2337" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2337" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="F2337" t="n">
+        <v>81.29000000000001</v>
+      </c>
+      <c r="G2337" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H2337" t="inlineStr"/>
+      <c r="I2337" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J2337" t="n">
+        <v>182</v>
+      </c>
+      <c r="K2337" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="L2337" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2338" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2338" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2338" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="F2338" t="n">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="G2338" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2338" t="inlineStr"/>
+      <c r="I2338" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J2338" t="n">
+        <v>61</v>
+      </c>
+      <c r="K2338" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L2338" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2339" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2339" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2339" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="F2339" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="G2339" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2339" t="inlineStr"/>
+      <c r="I2339" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J2339" t="n">
+        <v>92</v>
+      </c>
+      <c r="K2339" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="L2339" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2340" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2340" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2340" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="F2340" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="G2340" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2340" t="inlineStr"/>
+      <c r="I2340" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J2340" t="n">
+        <v>123</v>
+      </c>
+      <c r="K2340" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="L2340" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2340"/>
+  <dimension ref="A1:L2345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97866,6 +97866,206 @@
         </is>
       </c>
     </row>
+    <row r="2341">
+      <c r="A2341" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2341" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2341" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="F2341" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="G2341" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2341" t="inlineStr"/>
+      <c r="I2341" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2341" t="n">
+        <v>244</v>
+      </c>
+      <c r="K2341" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="L2341" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2342" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F2342" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="G2342" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2342" t="inlineStr"/>
+      <c r="I2342" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2342" t="n">
+        <v>171</v>
+      </c>
+      <c r="K2342" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="L2342" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2343" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="F2343" t="n">
+        <v>74.68000000000001</v>
+      </c>
+      <c r="G2343" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2343" t="inlineStr"/>
+      <c r="I2343" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2343" t="n">
+        <v>62</v>
+      </c>
+      <c r="K2343" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="L2343" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2344" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="F2344" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="G2344" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2344" t="inlineStr"/>
+      <c r="I2344" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2344" t="n">
+        <v>96</v>
+      </c>
+      <c r="K2344" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="L2344" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2345" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="F2345" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="G2345" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2345" t="inlineStr"/>
+      <c r="I2345" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2345" t="n">
+        <v>124</v>
+      </c>
+      <c r="K2345" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="L2345" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2345"/>
+  <dimension ref="A1:L2350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98066,6 +98066,206 @@
         </is>
       </c>
     </row>
+    <row r="2346">
+      <c r="A2346" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2346" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="F2346" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="G2346" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2346" t="inlineStr"/>
+      <c r="I2346" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2346" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2346" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="L2346" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2347" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2347" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2347" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F2347" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="G2347" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2347" t="inlineStr"/>
+      <c r="I2347" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J2347" t="n">
+        <v>163</v>
+      </c>
+      <c r="K2347" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="L2347" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2348" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2348" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2348" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="F2348" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="G2348" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2348" t="inlineStr"/>
+      <c r="I2348" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2348" t="n">
+        <v>93</v>
+      </c>
+      <c r="K2348" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="L2348" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2349" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>70.86</v>
+      </c>
+      <c r="G2349" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2349" t="inlineStr"/>
+      <c r="I2349" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2349" t="n">
+        <v>113</v>
+      </c>
+      <c r="K2349" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L2349" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2350" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2350" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="G2350" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2350" t="inlineStr"/>
+      <c r="I2350" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2350" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2350" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="L2350" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2350"/>
+  <dimension ref="A1:L2355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98266,6 +98266,206 @@
         </is>
       </c>
     </row>
+    <row r="2351">
+      <c r="A2351" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2351" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>71</v>
+      </c>
+      <c r="G2351" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2351" t="inlineStr"/>
+      <c r="I2351" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J2351" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2351" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="L2351" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2352" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F2352" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="G2352" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2352" t="inlineStr"/>
+      <c r="I2352" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J2352" t="n">
+        <v>168</v>
+      </c>
+      <c r="K2352" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="L2352" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2353" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2353" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2353" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F2353" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="G2353" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2353" t="inlineStr"/>
+      <c r="I2353" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J2353" t="n">
+        <v>38</v>
+      </c>
+      <c r="K2353" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="L2353" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2354" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="F2354" t="n">
+        <v>74</v>
+      </c>
+      <c r="G2354" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2354" t="inlineStr"/>
+      <c r="I2354" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J2354" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2354" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="L2354" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2355" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="F2355" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G2355" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2355" t="inlineStr"/>
+      <c r="I2355" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J2355" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2355" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="L2355" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2355"/>
+  <dimension ref="A1:L2360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98466,6 +98466,206 @@
         </is>
       </c>
     </row>
+    <row r="2356">
+      <c r="A2356" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2356" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2356" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2356" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="F2356" t="n">
+        <v>69.56999999999999</v>
+      </c>
+      <c r="G2356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2356" t="inlineStr"/>
+      <c r="I2356" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J2356" t="n">
+        <v>207</v>
+      </c>
+      <c r="K2356" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="L2356" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2357" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2357" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2357" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="F2357" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="G2357" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2357" t="inlineStr"/>
+      <c r="I2357" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="J2357" t="n">
+        <v>178</v>
+      </c>
+      <c r="K2357" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="L2357" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2358" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2358" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2358" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="F2358" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="G2358" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2358" t="inlineStr"/>
+      <c r="I2358" t="n">
+        <v>40</v>
+      </c>
+      <c r="J2358" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2358" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L2358" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2359" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2359" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2359" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="F2359" t="n">
+        <v>72.86</v>
+      </c>
+      <c r="G2359" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2359" t="inlineStr"/>
+      <c r="I2359" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J2359" t="n">
+        <v>88</v>
+      </c>
+      <c r="K2359" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="L2359" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2360" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2360" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2360" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="F2360" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="G2360" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2360" t="inlineStr"/>
+      <c r="I2360" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J2360" t="n">
+        <v>119</v>
+      </c>
+      <c r="K2360" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L2360" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2360"/>
+  <dimension ref="A1:L2365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98666,6 +98666,206 @@
         </is>
       </c>
     </row>
+    <row r="2361">
+      <c r="A2361" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2361" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2361" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2361" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="F2361" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="G2361" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2361" t="inlineStr"/>
+      <c r="I2361" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J2361" t="n">
+        <v>207</v>
+      </c>
+      <c r="K2361" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="L2361" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2362" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2362" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2362" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F2362" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="G2362" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2362" t="inlineStr"/>
+      <c r="I2362" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="J2362" t="n">
+        <v>182</v>
+      </c>
+      <c r="K2362" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="L2362" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2363" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2363" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2363" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="F2363" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="G2363" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2363" t="inlineStr"/>
+      <c r="I2363" t="n">
+        <v>40</v>
+      </c>
+      <c r="J2363" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2363" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="L2363" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2364" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2364" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2364" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F2364" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="G2364" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2364" t="inlineStr"/>
+      <c r="I2364" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="J2364" t="n">
+        <v>93</v>
+      </c>
+      <c r="K2364" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="L2364" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2365" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2365" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2365" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="F2365" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="G2365" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2365" t="inlineStr"/>
+      <c r="I2365" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="J2365" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2365" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="L2365" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2365"/>
+  <dimension ref="A1:L2370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98866,6 +98866,206 @@
         </is>
       </c>
     </row>
+    <row r="2366">
+      <c r="A2366" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2366" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2366" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2366" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="F2366" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="G2366" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2366" t="inlineStr"/>
+      <c r="I2366" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J2366" t="n">
+        <v>188</v>
+      </c>
+      <c r="K2366" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="L2366" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2367" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2367" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2367" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="F2367" t="n">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="G2367" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2367" t="inlineStr"/>
+      <c r="I2367" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J2367" t="n">
+        <v>142</v>
+      </c>
+      <c r="K2367" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="L2367" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2368" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2368" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2368" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="F2368" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="G2368" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2368" t="inlineStr"/>
+      <c r="I2368" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2368" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2368" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="L2368" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2369" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2369" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2369" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F2369" t="n">
+        <v>67.33</v>
+      </c>
+      <c r="G2369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2369" t="inlineStr"/>
+      <c r="I2369" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2369" t="n">
+        <v>96</v>
+      </c>
+      <c r="K2369" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="L2369" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2370" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2370" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2370" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2370" t="n">
+        <v>63.62</v>
+      </c>
+      <c r="G2370" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2370" t="inlineStr"/>
+      <c r="I2370" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J2370" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2370" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L2370" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2370"/>
+  <dimension ref="A1:L2375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99066,6 +99066,206 @@
         </is>
       </c>
     </row>
+    <row r="2371">
+      <c r="A2371" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2371" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2371" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2371" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="F2371" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="G2371" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2371" t="inlineStr"/>
+      <c r="I2371" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J2371" t="n">
+        <v>188</v>
+      </c>
+      <c r="K2371" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="L2371" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2372" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2372" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2372" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F2372" t="n">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="G2372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2372" t="inlineStr"/>
+      <c r="I2372" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2372" t="n">
+        <v>126</v>
+      </c>
+      <c r="K2372" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="L2372" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2373" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2373" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2373" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F2373" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="G2373" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2373" t="inlineStr"/>
+      <c r="I2373" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="J2373" t="n">
+        <v>121</v>
+      </c>
+      <c r="K2373" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="L2373" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2374" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2374" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2374" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="F2374" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="G2374" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2374" t="inlineStr"/>
+      <c r="I2374" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="J2374" t="n">
+        <v>93</v>
+      </c>
+      <c r="K2374" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L2374" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2375" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2375" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2375" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2375" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="G2375" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2375" t="inlineStr"/>
+      <c r="I2375" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2375" t="n">
+        <v>108</v>
+      </c>
+      <c r="K2375" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="L2375" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2375"/>
+  <dimension ref="A1:L2380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99266,6 +99266,206 @@
         </is>
       </c>
     </row>
+    <row r="2376">
+      <c r="A2376" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2376" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2376" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2376" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="F2376" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="G2376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2376" t="inlineStr"/>
+      <c r="I2376" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2376" t="n">
+        <v>184</v>
+      </c>
+      <c r="K2376" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L2376" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2377" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2377" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2377" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="F2377" t="n">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="G2377" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2377" t="inlineStr"/>
+      <c r="I2377" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2377" t="n">
+        <v>143</v>
+      </c>
+      <c r="K2377" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="L2377" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2378" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2378" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2378" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F2378" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="G2378" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2378" t="inlineStr"/>
+      <c r="I2378" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2378" t="n">
+        <v>28</v>
+      </c>
+      <c r="K2378" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="L2378" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2379" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2379" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2379" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="F2379" t="n">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="G2379" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2379" t="inlineStr"/>
+      <c r="I2379" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2379" t="n">
+        <v>70</v>
+      </c>
+      <c r="K2379" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="L2379" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2380" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2380" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2380" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="F2380" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="G2380" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2380" t="inlineStr"/>
+      <c r="I2380" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2380" t="n">
+        <v>104</v>
+      </c>
+      <c r="K2380" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L2380" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2380"/>
+  <dimension ref="A1:L2385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99466,6 +99466,206 @@
         </is>
       </c>
     </row>
+    <row r="2381">
+      <c r="A2381" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2381" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2381" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2381" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F2381" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="G2381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2381" t="inlineStr"/>
+      <c r="I2381" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2381" t="n">
+        <v>132</v>
+      </c>
+      <c r="K2381" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="L2381" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2382" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2382" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2382" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F2382" t="n">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="G2382" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2382" t="inlineStr"/>
+      <c r="I2382" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J2382" t="n">
+        <v>150</v>
+      </c>
+      <c r="K2382" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="L2382" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2383" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2383" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2383" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="F2383" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G2383" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2383" t="inlineStr"/>
+      <c r="I2383" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="J2383" t="n">
+        <v>51</v>
+      </c>
+      <c r="K2383" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="L2383" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2384" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2384" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2384" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F2384" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="G2384" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2384" t="inlineStr"/>
+      <c r="I2384" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="J2384" t="n">
+        <v>109</v>
+      </c>
+      <c r="K2384" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="L2384" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2385" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2385" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2385" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="F2385" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="G2385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2385" t="inlineStr"/>
+      <c r="I2385" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J2385" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2385" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="L2385" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2385"/>
+  <dimension ref="A1:L2390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99666,6 +99666,206 @@
         </is>
       </c>
     </row>
+    <row r="2386">
+      <c r="A2386" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2386" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2386" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2386" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="F2386" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="G2386" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2386" t="inlineStr"/>
+      <c r="I2386" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J2386" t="n">
+        <v>186</v>
+      </c>
+      <c r="K2386" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="L2386" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2387" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2387" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2387" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="F2387" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="G2387" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2387" t="inlineStr"/>
+      <c r="I2387" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J2387" t="n">
+        <v>140</v>
+      </c>
+      <c r="K2387" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="L2387" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2388" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2388" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2388" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="F2388" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="G2388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2388" t="inlineStr"/>
+      <c r="I2388" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J2388" t="n">
+        <v>127</v>
+      </c>
+      <c r="K2388" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="L2388" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2389" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2389" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2389" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="F2389" t="n">
+        <v>65.16</v>
+      </c>
+      <c r="G2389" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2389" t="inlineStr"/>
+      <c r="I2389" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J2389" t="n">
+        <v>103</v>
+      </c>
+      <c r="K2389" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="L2389" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2390" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2390" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2390" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="F2390" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="G2390" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2390" t="inlineStr"/>
+      <c r="I2390" t="n">
+        <v>22</v>
+      </c>
+      <c r="J2390" t="n">
+        <v>126</v>
+      </c>
+      <c r="K2390" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="L2390" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2390"/>
+  <dimension ref="A1:L2395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99866,6 +99866,206 @@
         </is>
       </c>
     </row>
+    <row r="2391">
+      <c r="A2391" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2391" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2391" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2391" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="F2391" t="n">
+        <v>67.67</v>
+      </c>
+      <c r="G2391" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2391" t="inlineStr"/>
+      <c r="I2391" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2391" t="n">
+        <v>186</v>
+      </c>
+      <c r="K2391" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="L2391" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2392" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2392" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2392" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="F2392" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G2392" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2392" t="inlineStr"/>
+      <c r="I2392" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J2392" t="n">
+        <v>189</v>
+      </c>
+      <c r="K2392" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="L2392" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2393" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2393" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2393" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="F2393" t="n">
+        <v>72.11</v>
+      </c>
+      <c r="G2393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2393" t="inlineStr"/>
+      <c r="I2393" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J2393" t="n">
+        <v>63</v>
+      </c>
+      <c r="K2393" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="L2393" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2394" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2394" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2394" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="F2394" t="n">
+        <v>67.28</v>
+      </c>
+      <c r="G2394" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2394" t="inlineStr"/>
+      <c r="I2394" t="n">
+        <v>22</v>
+      </c>
+      <c r="J2394" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2394" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="L2394" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2395" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2395" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2395" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2395" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="G2395" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2395" t="inlineStr"/>
+      <c r="I2395" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J2395" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2395" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="L2395" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2395"/>
+  <dimension ref="A1:L2400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100066,6 +100066,206 @@
         </is>
       </c>
     </row>
+    <row r="2396">
+      <c r="A2396" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2396" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2396" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2396" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F2396" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G2396" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2396" t="inlineStr"/>
+      <c r="I2396" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2396" t="n">
+        <v>23</v>
+      </c>
+      <c r="K2396" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="L2396" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2397" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2397" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2397" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="F2397" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G2397" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2397" t="inlineStr"/>
+      <c r="I2397" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2397" t="n">
+        <v>204</v>
+      </c>
+      <c r="K2397" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="L2397" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2398" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2398" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2398" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F2398" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="G2398" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2398" t="inlineStr"/>
+      <c r="I2398" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2398" t="n">
+        <v>62</v>
+      </c>
+      <c r="K2398" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="L2398" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2399" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2399" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2399" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F2399" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G2399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2399" t="inlineStr"/>
+      <c r="I2399" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2399" t="n">
+        <v>108</v>
+      </c>
+      <c r="K2399" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="L2399" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2400" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2400" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2400" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F2400" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="G2400" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2400" t="inlineStr"/>
+      <c r="I2400" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2400" t="n">
+        <v>126</v>
+      </c>
+      <c r="K2400" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="L2400" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2400"/>
+  <dimension ref="A1:L2405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100266,6 +100266,206 @@
         </is>
       </c>
     </row>
+    <row r="2401">
+      <c r="A2401" s="1" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2401" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2401" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2401" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="F2401" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="G2401" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2401" t="inlineStr"/>
+      <c r="I2401" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J2401" t="n">
+        <v>182</v>
+      </c>
+      <c r="K2401" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L2401" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" s="1" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2402" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2402" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2402" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="F2402" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="G2402" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2402" t="inlineStr"/>
+      <c r="I2402" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J2402" t="n">
+        <v>131</v>
+      </c>
+      <c r="K2402" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="L2402" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" s="1" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2403" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2403" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2403" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="F2403" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="G2403" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2403" t="inlineStr"/>
+      <c r="I2403" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="J2403" t="n">
+        <v>62</v>
+      </c>
+      <c r="K2403" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="L2403" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" s="1" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2404" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2404" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2404" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F2404" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="G2404" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2404" t="inlineStr"/>
+      <c r="I2404" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J2404" t="n">
+        <v>87</v>
+      </c>
+      <c r="K2404" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="L2404" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" s="1" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2405" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2405" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2405" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="F2405" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="G2405" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2405" t="inlineStr"/>
+      <c r="I2405" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J2405" t="n">
+        <v>123</v>
+      </c>
+      <c r="K2405" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="L2405" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2405"/>
+  <dimension ref="A1:L2410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100466,6 +100466,206 @@
         </is>
       </c>
     </row>
+    <row r="2406">
+      <c r="A2406" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2406" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2406" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2406" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F2406" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="G2406" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2406" t="inlineStr"/>
+      <c r="I2406" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2406" t="n">
+        <v>194</v>
+      </c>
+      <c r="K2406" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="L2406" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2407" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2407" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2407" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="F2407" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="G2407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2407" t="inlineStr"/>
+      <c r="I2407" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2407" t="n">
+        <v>151</v>
+      </c>
+      <c r="K2407" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="L2407" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2408" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2408" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2408" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F2408" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="G2408" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2408" t="inlineStr"/>
+      <c r="I2408" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2408" t="n">
+        <v>54</v>
+      </c>
+      <c r="K2408" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L2408" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2409" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2409" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2409" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="F2409" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="G2409" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2409" t="inlineStr"/>
+      <c r="I2409" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2409" t="n">
+        <v>86</v>
+      </c>
+      <c r="K2409" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="L2409" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2410" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2410" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2410" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="F2410" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G2410" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2410" t="inlineStr"/>
+      <c r="I2410" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2410" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2410" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="L2410" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2410"/>
+  <dimension ref="A1:L2415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100666,6 +100666,206 @@
         </is>
       </c>
     </row>
+    <row r="2411">
+      <c r="A2411" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2411" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2411" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2411" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F2411" t="n">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="G2411" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2411" t="inlineStr"/>
+      <c r="I2411" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2411" t="n">
+        <v>216</v>
+      </c>
+      <c r="K2411" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="L2411" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2412" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2412" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2412" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="F2412" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="G2412" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2412" t="inlineStr"/>
+      <c r="I2412" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2412" t="n">
+        <v>151</v>
+      </c>
+      <c r="K2412" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="L2412" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2413" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2413" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2413" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F2413" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="G2413" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2413" t="inlineStr"/>
+      <c r="I2413" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2413" t="n">
+        <v>34</v>
+      </c>
+      <c r="K2413" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="L2413" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2414" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2414" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2414" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F2414" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="G2414" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2414" t="inlineStr"/>
+      <c r="I2414" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2414" t="n">
+        <v>88</v>
+      </c>
+      <c r="K2414" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="L2414" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2415" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2415" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2415" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="F2415" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G2415" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2415" t="inlineStr"/>
+      <c r="I2415" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2415" t="n">
+        <v>114</v>
+      </c>
+      <c r="K2415" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="L2415" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2415"/>
+  <dimension ref="A1:L2420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100866,6 +100866,206 @@
         </is>
       </c>
     </row>
+    <row r="2416">
+      <c r="A2416" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2416" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2416" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2416" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="F2416" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="G2416" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2416" t="inlineStr"/>
+      <c r="I2416" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="J2416" t="n">
+        <v>198</v>
+      </c>
+      <c r="K2416" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="L2416" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2417" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2417" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2417" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="F2417" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="G2417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2417" t="inlineStr"/>
+      <c r="I2417" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J2417" t="n">
+        <v>144</v>
+      </c>
+      <c r="K2417" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="L2417" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2418" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2418" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2418" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="F2418" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="G2418" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2418" t="inlineStr"/>
+      <c r="I2418" t="n">
+        <v>17</v>
+      </c>
+      <c r="J2418" t="n">
+        <v>30</v>
+      </c>
+      <c r="K2418" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="L2418" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2419" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2419" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2419" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="F2419" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="G2419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2419" t="inlineStr"/>
+      <c r="I2419" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="J2419" t="n">
+        <v>93</v>
+      </c>
+      <c r="K2419" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="L2419" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2420" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2420" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2420" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F2420" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="G2420" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2420" t="inlineStr"/>
+      <c r="I2420" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J2420" t="n">
+        <v>103</v>
+      </c>
+      <c r="K2420" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="L2420" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2420"/>
+  <dimension ref="A1:L2425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101066,6 +101066,206 @@
         </is>
       </c>
     </row>
+    <row r="2421">
+      <c r="A2421" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2421" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2421" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2421" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="F2421" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="G2421" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2421" t="inlineStr"/>
+      <c r="I2421" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2421" t="n">
+        <v>193</v>
+      </c>
+      <c r="K2421" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="L2421" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2422" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2422" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2422" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="F2422" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="G2422" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2422" t="inlineStr"/>
+      <c r="I2422" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J2422" t="n">
+        <v>145</v>
+      </c>
+      <c r="K2422" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="L2422" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2423" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2423" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2423" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F2423" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="G2423" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2423" t="inlineStr"/>
+      <c r="I2423" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J2423" t="n">
+        <v>34</v>
+      </c>
+      <c r="K2423" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="L2423" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2424" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2424" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2424" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="F2424" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="G2424" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2424" t="inlineStr"/>
+      <c r="I2424" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J2424" t="n">
+        <v>84</v>
+      </c>
+      <c r="K2424" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="L2424" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2425" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2425" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2425" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F2425" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="G2425" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2425" t="inlineStr"/>
+      <c r="I2425" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J2425" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2425" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="L2425" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2425"/>
+  <dimension ref="A1:L2430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101266,6 +101266,206 @@
         </is>
       </c>
     </row>
+    <row r="2426">
+      <c r="A2426" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2426" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2426" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2426" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="F2426" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="G2426" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2426" t="inlineStr"/>
+      <c r="I2426" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2426" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2426" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="L2426" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2427" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2427" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2427" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F2427" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="G2427" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2427" t="inlineStr"/>
+      <c r="I2427" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2427" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2427" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="L2427" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2428" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2428" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2428" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F2428" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="G2428" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2428" t="inlineStr"/>
+      <c r="I2428" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J2428" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2428" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="L2428" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2429" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2429" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2429" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F2429" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="G2429" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2429" t="inlineStr"/>
+      <c r="I2429" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2429" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2429" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="L2429" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2430" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2430" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2430" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="F2430" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="G2430" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2430" t="inlineStr"/>
+      <c r="I2430" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2430" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2430" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="L2430" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2430"/>
+  <dimension ref="A1:L2435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101466,6 +101466,206 @@
         </is>
       </c>
     </row>
+    <row r="2431">
+      <c r="A2431" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2431" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2431" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2431" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="F2431" t="n">
+        <v>68.23999999999999</v>
+      </c>
+      <c r="G2431" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2431" t="inlineStr"/>
+      <c r="I2431" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J2431" t="n">
+        <v>127</v>
+      </c>
+      <c r="K2431" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L2431" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2432" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2432" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2432" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="F2432" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="G2432" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2432" t="inlineStr"/>
+      <c r="I2432" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J2432" t="n">
+        <v>115</v>
+      </c>
+      <c r="K2432" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="L2432" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2433" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2433" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2433" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="F2433" t="n">
+        <v>68.86</v>
+      </c>
+      <c r="G2433" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2433" t="inlineStr"/>
+      <c r="I2433" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="J2433" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2433" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="L2433" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2434" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2434" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2434" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="F2434" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G2434" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2434" t="inlineStr"/>
+      <c r="I2434" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="J2434" t="n">
+        <v>104</v>
+      </c>
+      <c r="K2434" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L2434" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2435" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2435" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2435" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="F2435" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G2435" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2435" t="inlineStr"/>
+      <c r="I2435" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="J2435" t="n">
+        <v>121</v>
+      </c>
+      <c r="K2435" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="L2435" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2435"/>
+  <dimension ref="A1:L2440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101666,6 +101666,206 @@
         </is>
       </c>
     </row>
+    <row r="2436">
+      <c r="A2436" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2436" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2436" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2436" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="F2436" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G2436" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2436" t="inlineStr"/>
+      <c r="I2436" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J2436" t="n">
+        <v>192</v>
+      </c>
+      <c r="K2436" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="L2436" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2437" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2437" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2437" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F2437" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G2437" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H2437" t="inlineStr"/>
+      <c r="I2437" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J2437" t="n">
+        <v>153</v>
+      </c>
+      <c r="K2437" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L2437" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2438" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2438" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2438" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="F2438" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="G2438" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2438" t="inlineStr"/>
+      <c r="I2438" t="n">
+        <v>22</v>
+      </c>
+      <c r="J2438" t="n">
+        <v>206</v>
+      </c>
+      <c r="K2438" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L2438" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2439" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2439" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2439" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="F2439" t="n">
+        <v>64</v>
+      </c>
+      <c r="G2439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2439" t="inlineStr"/>
+      <c r="I2439" t="n">
+        <v>41</v>
+      </c>
+      <c r="J2439" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2439" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="L2439" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2440" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2440" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2440" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F2440" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="G2440" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2440" t="inlineStr"/>
+      <c r="I2440" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J2440" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2440" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="L2440" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2440"/>
+  <dimension ref="A1:L2445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101866,6 +101866,206 @@
         </is>
       </c>
     </row>
+    <row r="2441">
+      <c r="A2441" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2441" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2441" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2441" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="F2441" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="G2441" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2441" t="inlineStr"/>
+      <c r="I2441" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2441" t="n">
+        <v>180</v>
+      </c>
+      <c r="K2441" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="L2441" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2442" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2442" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2442" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="F2442" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="G2442" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2442" t="inlineStr"/>
+      <c r="I2442" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2442" t="n">
+        <v>154</v>
+      </c>
+      <c r="K2442" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="L2442" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2443" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2443" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2443" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="F2443" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G2443" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2443" t="inlineStr"/>
+      <c r="I2443" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2443" t="n">
+        <v>108</v>
+      </c>
+      <c r="K2443" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="L2443" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2444" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2444" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2444" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F2444" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="G2444" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2444" t="inlineStr"/>
+      <c r="I2444" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2444" t="n">
+        <v>92</v>
+      </c>
+      <c r="K2444" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="L2444" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2445" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2445" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2445" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="G2445" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2445" t="inlineStr"/>
+      <c r="I2445" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2445" t="n">
+        <v>103</v>
+      </c>
+      <c r="K2445" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="L2445" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2445"/>
+  <dimension ref="A1:L2450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102066,6 +102066,206 @@
         </is>
       </c>
     </row>
+    <row r="2446">
+      <c r="A2446" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2446" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2446" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2446" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="F2446" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="G2446" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2446" t="inlineStr"/>
+      <c r="I2446" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="J2446" t="n">
+        <v>184</v>
+      </c>
+      <c r="K2446" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="L2446" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2447" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2447" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2447" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="F2447" t="n">
+        <v>83.29000000000001</v>
+      </c>
+      <c r="G2447" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2447" t="inlineStr"/>
+      <c r="I2447" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2447" t="n">
+        <v>156</v>
+      </c>
+      <c r="K2447" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="L2447" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2448" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2448" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2448" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="F2448" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="G2448" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2448" t="inlineStr"/>
+      <c r="I2448" t="n">
+        <v>27</v>
+      </c>
+      <c r="J2448" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2448" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="L2448" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2449" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2449" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2449" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F2449" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="G2449" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2449" t="inlineStr"/>
+      <c r="I2449" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J2449" t="n">
+        <v>80</v>
+      </c>
+      <c r="K2449" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L2449" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2450" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2450" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2450" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F2450" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="G2450" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2450" t="inlineStr"/>
+      <c r="I2450" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J2450" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2450" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="L2450" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2450"/>
+  <dimension ref="A1:L2455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102266,6 +102266,206 @@
         </is>
       </c>
     </row>
+    <row r="2451">
+      <c r="A2451" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2451" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2451" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2451" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="F2451" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="G2451" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2451" t="inlineStr"/>
+      <c r="I2451" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="J2451" t="n">
+        <v>120</v>
+      </c>
+      <c r="K2451" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="L2451" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2452" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2452" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2452" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="F2452" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="G2452" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2452" t="inlineStr"/>
+      <c r="I2452" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J2452" t="n">
+        <v>118</v>
+      </c>
+      <c r="K2452" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="L2452" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2453" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2453" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2453" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="F2453" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="G2453" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2453" t="inlineStr"/>
+      <c r="I2453" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J2453" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2453" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="L2453" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2454" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2454" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2454" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F2454" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="G2454" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2454" t="inlineStr"/>
+      <c r="I2454" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J2454" t="n">
+        <v>118</v>
+      </c>
+      <c r="K2454" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="L2454" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2455" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2455" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2455" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="F2455" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="G2455" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2455" t="inlineStr"/>
+      <c r="I2455" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="J2455" t="n">
+        <v>113</v>
+      </c>
+      <c r="K2455" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="L2455" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2455"/>
+  <dimension ref="A1:L2460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102466,6 +102466,206 @@
         </is>
       </c>
     </row>
+    <row r="2456">
+      <c r="A2456" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2456" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2456" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2456" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F2456" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G2456" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2456" t="inlineStr"/>
+      <c r="I2456" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="J2456" t="n">
+        <v>186</v>
+      </c>
+      <c r="K2456" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="L2456" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2457" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2457" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2457" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F2457" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G2457" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2457" t="inlineStr"/>
+      <c r="I2457" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2457" t="n">
+        <v>151</v>
+      </c>
+      <c r="K2457" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="L2457" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2458" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2458" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2458" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="F2458" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="G2458" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2458" t="inlineStr"/>
+      <c r="I2458" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J2458" t="n">
+        <v>45</v>
+      </c>
+      <c r="K2458" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L2458" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2459" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2459" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2459" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F2459" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="G2459" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2459" t="inlineStr"/>
+      <c r="I2459" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J2459" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2459" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="L2459" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2460" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2460" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2460" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="F2460" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="G2460" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2460" t="inlineStr"/>
+      <c r="I2460" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J2460" t="n">
+        <v>109</v>
+      </c>
+      <c r="K2460" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="L2460" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2460"/>
+  <dimension ref="A1:L2465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102666,6 +102666,206 @@
         </is>
       </c>
     </row>
+    <row r="2461">
+      <c r="A2461" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2461" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2461" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2461" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F2461" t="n">
+        <v>66.84999999999999</v>
+      </c>
+      <c r="G2461" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2461" t="inlineStr"/>
+      <c r="I2461" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="J2461" t="n">
+        <v>182</v>
+      </c>
+      <c r="K2461" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="L2461" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2462" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2462" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2462" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F2462" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G2462" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2462" t="inlineStr"/>
+      <c r="I2462" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J2462" t="n">
+        <v>142</v>
+      </c>
+      <c r="K2462" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="L2462" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2463" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2463" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2463" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F2463" t="n">
+        <v>66.84999999999999</v>
+      </c>
+      <c r="G2463" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2463" t="inlineStr"/>
+      <c r="I2463" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J2463" t="n">
+        <v>70</v>
+      </c>
+      <c r="K2463" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="L2463" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2464" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2464" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2464" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2464" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="G2464" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2464" t="inlineStr"/>
+      <c r="I2464" t="n">
+        <v>39</v>
+      </c>
+      <c r="J2464" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2464" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="L2464" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2465" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2465" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2465" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F2465" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="G2465" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2465" t="inlineStr"/>
+      <c r="I2465" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J2465" t="n">
+        <v>116</v>
+      </c>
+      <c r="K2465" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="L2465" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2465"/>
+  <dimension ref="A1:L2470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102866,6 +102866,206 @@
         </is>
       </c>
     </row>
+    <row r="2466">
+      <c r="A2466" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2466" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2466" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2466" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="F2466" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G2466" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2466" t="inlineStr"/>
+      <c r="I2466" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="J2466" t="n">
+        <v>191</v>
+      </c>
+      <c r="K2466" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="L2466" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2467" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2467" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2467" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="F2467" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="G2467" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2467" t="inlineStr"/>
+      <c r="I2467" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J2467" t="n">
+        <v>149</v>
+      </c>
+      <c r="K2467" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="L2467" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2468" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2468" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2468" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="F2468" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="G2468" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2468" t="inlineStr"/>
+      <c r="I2468" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="J2468" t="n">
+        <v>59</v>
+      </c>
+      <c r="K2468" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L2468" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2469" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2469" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2469" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F2469" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="G2469" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2469" t="inlineStr"/>
+      <c r="I2469" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J2469" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2469" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="L2469" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2470" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2470" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2470" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F2470" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="G2470" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2470" t="inlineStr"/>
+      <c r="I2470" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="J2470" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2470" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="L2470" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
